--- a/doc/excel/화면설계서_X1_항공편검색.xlsx
+++ b/doc/excel/화면설계서_X1_항공편검색.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lee\Desktop\hoshimoto\02_projects\loveMyself\doc\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\gwx\java\SpringLab01\doc\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8AAD964-A2DD-4B10-9E20-4CDBDEDD6FE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49ED7617-D794-417E-B1EF-7FA7FF1E2FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1890" yWindow="1950" windowWidth="20295" windowHeight="12060" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="1" r:id="rId1"/>
@@ -363,12 +363,6 @@
     <t>항목 No.9 「−」「＋」 클릭</t>
   </si>
   <si>
-    <t>・성인 인원을 1 증감한다.
-・성인 인원이 1일 때 「−」를 비활성화한다.
-・성인 인원과 유아 인원의 합계가 9일 때 「＋」를 비활성화한다.
-・성인 인원이 유아 인원과 같을 때 「−」를 비활성화한다.</t>
-  </si>
-  <si>
     <t>유아 인원 증감</t>
   </si>
   <si>
@@ -733,12 +727,495 @@
   <si>
     <t>사용API 시트 신규 추가(X0 공항 목록 조회, X1 항공편 검색)</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인원을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>증감한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인원이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 「−」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비활성화한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인원과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인원의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>합계가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>일</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 「＋」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비활성화한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.
+・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>성인</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인원이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>유아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>인원과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>같을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> 「−」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>비활성화한다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -809,8 +1286,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -830,6 +1325,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -898,46 +1399,64 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -949,29 +1468,21 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1317,13 +1828,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="E8:AJ29"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="5:36">
-      <c r="E8" s="4" t="s">
+    <row r="8" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="E8" s="11" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="3"/>
@@ -1358,7 +1869,7 @@
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
     </row>
-    <row r="9" spans="5:36">
+    <row r="9" spans="5:36" x14ac:dyDescent="0.15">
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
@@ -1392,7 +1903,7 @@
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
     </row>
-    <row r="10" spans="5:36">
+    <row r="10" spans="5:36" x14ac:dyDescent="0.15">
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
@@ -1426,146 +1937,146 @@
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
     </row>
-    <row r="12" spans="5:36">
-      <c r="E12" s="7" t="s">
+    <row r="12" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="E12" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="8"/>
-      <c r="AH12" s="8"/>
-      <c r="AI12" s="8"/>
-      <c r="AJ12" s="8"/>
-    </row>
-    <row r="13" spans="5:36">
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="8"/>
-      <c r="AB13" s="8"/>
-      <c r="AC13" s="8"/>
-      <c r="AD13" s="8"/>
-      <c r="AE13" s="8"/>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="8"/>
-      <c r="AH13" s="8"/>
-      <c r="AI13" s="8"/>
-      <c r="AJ13" s="8"/>
-    </row>
-    <row r="14" spans="5:36">
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8"/>
-      <c r="AA14" s="8"/>
-      <c r="AB14" s="8"/>
-      <c r="AC14" s="8"/>
-      <c r="AD14" s="8"/>
-      <c r="AE14" s="8"/>
-      <c r="AF14" s="8"/>
-      <c r="AG14" s="8"/>
-      <c r="AH14" s="8"/>
-      <c r="AI14" s="8"/>
-      <c r="AJ14" s="8"/>
-    </row>
-    <row r="15" spans="5:36">
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="8"/>
-      <c r="AB15" s="8"/>
-      <c r="AC15" s="8"/>
-      <c r="AD15" s="8"/>
-      <c r="AE15" s="8"/>
-      <c r="AF15" s="8"/>
-      <c r="AG15" s="8"/>
-      <c r="AH15" s="8"/>
-      <c r="AI15" s="8"/>
-      <c r="AJ15" s="8"/>
-    </row>
-    <row r="17" spans="5:36">
-      <c r="E17" s="4" t="s">
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="13"/>
+      <c r="AF12" s="13"/>
+      <c r="AG12" s="13"/>
+      <c r="AH12" s="13"/>
+      <c r="AI12" s="13"/>
+      <c r="AJ12" s="13"/>
+    </row>
+    <row r="13" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="13"/>
+      <c r="P13" s="13"/>
+      <c r="Q13" s="13"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="13"/>
+      <c r="U13" s="13"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="13"/>
+      <c r="AF13" s="13"/>
+      <c r="AG13" s="13"/>
+      <c r="AH13" s="13"/>
+      <c r="AI13" s="13"/>
+      <c r="AJ13" s="13"/>
+    </row>
+    <row r="14" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="13"/>
+      <c r="P14" s="13"/>
+      <c r="Q14" s="13"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="13"/>
+      <c r="U14" s="13"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="13"/>
+      <c r="AD14" s="13"/>
+      <c r="AE14" s="13"/>
+      <c r="AF14" s="13"/>
+      <c r="AG14" s="13"/>
+      <c r="AH14" s="13"/>
+      <c r="AI14" s="13"/>
+      <c r="AJ14" s="13"/>
+    </row>
+    <row r="15" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13"/>
+      <c r="O15" s="13"/>
+      <c r="P15" s="13"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="13"/>
+      <c r="U15" s="13"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="13"/>
+      <c r="AC15" s="13"/>
+      <c r="AD15" s="13"/>
+      <c r="AE15" s="13"/>
+      <c r="AF15" s="13"/>
+      <c r="AG15" s="13"/>
+      <c r="AH15" s="13"/>
+      <c r="AI15" s="13"/>
+      <c r="AJ15" s="13"/>
+    </row>
+    <row r="17" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="E17" s="11" t="s">
         <v>2</v>
       </c>
       <c r="F17" s="3"/>
@@ -1600,7 +2111,7 @@
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
     </row>
-    <row r="18" spans="5:36">
+    <row r="18" spans="5:36" x14ac:dyDescent="0.15">
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -1634,16 +2145,16 @@
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
     </row>
-    <row r="22" spans="5:36">
-      <c r="M22" s="5" t="s">
+    <row r="22" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="M22" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="2" t="s">
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="10" t="s">
         <v>4</v>
       </c>
       <c r="T22" s="3"/>
@@ -1656,13 +2167,13 @@
       <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
     </row>
-    <row r="23" spans="5:36">
-      <c r="M23" s="6"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="6"/>
-      <c r="R23" s="6"/>
+    <row r="23" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -1674,16 +2185,16 @@
       <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
     </row>
-    <row r="24" spans="5:36">
-      <c r="M24" s="5" t="s">
+    <row r="24" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="M24" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="2" t="s">
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="10" t="s">
         <v>6</v>
       </c>
       <c r="T24" s="3"/>
@@ -1696,13 +2207,13 @@
       <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
     </row>
-    <row r="25" spans="5:36">
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6"/>
-      <c r="R25" s="6"/>
+    <row r="25" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -1714,16 +2225,16 @@
       <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
     </row>
-    <row r="26" spans="5:36">
-      <c r="M26" s="5" t="s">
+    <row r="26" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="M26" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
-      <c r="R26" s="6"/>
-      <c r="S26" s="2"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
+      <c r="S26" s="10"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -1734,13 +2245,13 @@
       <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
     </row>
-    <row r="27" spans="5:36">
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
+    <row r="27" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -1752,16 +2263,16 @@
       <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
     </row>
-    <row r="28" spans="5:36">
-      <c r="M28" s="5" t="s">
+    <row r="28" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="M28" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="2"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="10"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
@@ -1772,13 +2283,13 @@
       <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
     </row>
-    <row r="29" spans="5:36">
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
+    <row r="29" spans="5:36" x14ac:dyDescent="0.15">
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
@@ -1792,17 +2303,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="S22:AB23"/>
+    <mergeCell ref="E17:AJ18"/>
+    <mergeCell ref="E8:AJ10"/>
+    <mergeCell ref="M22:R23"/>
+    <mergeCell ref="E12:AJ15"/>
     <mergeCell ref="M28:R29"/>
     <mergeCell ref="S24:AB25"/>
     <mergeCell ref="M26:R27"/>
     <mergeCell ref="M24:R25"/>
     <mergeCell ref="S26:AB27"/>
     <mergeCell ref="S28:AB29"/>
-    <mergeCell ref="S22:AB23"/>
-    <mergeCell ref="E17:AJ18"/>
-    <mergeCell ref="E8:AJ10"/>
-    <mergeCell ref="M22:R23"/>
-    <mergeCell ref="E12:AJ15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1816,13 +2327,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN14"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="3"/>
@@ -1832,13 +2343,13 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="13" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -1854,13 +2365,13 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="9" t="s">
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -1873,7 +2384,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1882,13 +2393,13 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -1904,13 +2415,13 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="9"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -1921,72 +2432,72 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="4" spans="1:40">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="11" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="11" t="s">
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="11" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="11" t="s">
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-    </row>
-    <row r="5" spans="1:40" ht="18" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+    </row>
+    <row r="5" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="6" t="s">
         <v>16</v>
       </c>
       <c r="J5" s="3"/>
@@ -1996,7 +2507,7 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-      <c r="Q5" s="10" t="s">
+      <c r="Q5" s="6" t="s">
         <v>17</v>
       </c>
       <c r="R5" s="3"/>
@@ -2016,15 +2527,15 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
-      <c r="AI5" s="9"/>
+      <c r="AI5" s="2"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
-    <row r="6" spans="1:40" ht="48" customHeight="1">
-      <c r="A6" s="9">
+    <row r="6" spans="1:40" ht="48" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
         <v>1.1000000000000001</v>
       </c>
       <c r="B6" s="3"/>
@@ -2036,8 +2547,8 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="10" t="s">
-        <v>185</v>
+      <c r="I6" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -2046,8 +2557,8 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-      <c r="Q6" s="10" t="s">
-        <v>186</v>
+      <c r="Q6" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -2066,15 +2577,15 @@
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
-      <c r="AI6" s="9"/>
+      <c r="AI6" s="2"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
     </row>
-    <row r="7" spans="1:40" ht="18" customHeight="1">
-      <c r="A7" s="9">
+    <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
         <v>1.2</v>
       </c>
       <c r="B7" s="3"/>
@@ -2086,8 +2597,8 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="10" t="s">
-        <v>187</v>
+      <c r="I7" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -2096,8 +2607,8 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-      <c r="Q7" s="10" t="s">
-        <v>215</v>
+      <c r="Q7" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -2116,23 +2627,23 @@
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
-      <c r="AI7" s="9"/>
+      <c r="AI7" s="2"/>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
     </row>
-    <row r="8" spans="1:40" ht="18" customHeight="1">
-      <c r="A8" s="9"/>
+    <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="9"/>
+      <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="10"/>
+      <c r="I8" s="6"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -2140,7 +2651,7 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-      <c r="Q8" s="10"/>
+      <c r="Q8" s="6"/>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -2158,23 +2669,23 @@
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="9"/>
+      <c r="AI8" s="2"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
-    <row r="9" spans="1:40" ht="18" customHeight="1">
-      <c r="A9" s="9"/>
+    <row r="9" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="9"/>
+      <c r="D9" s="2"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="10"/>
+      <c r="I9" s="6"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -2182,7 +2693,7 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="10"/>
+      <c r="Q9" s="6"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -2200,23 +2711,23 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
-      <c r="AI9" s="9"/>
+      <c r="AI9" s="2"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
     </row>
-    <row r="10" spans="1:40" ht="18" customHeight="1">
-      <c r="A10" s="9"/>
+    <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="9"/>
+      <c r="D10" s="2"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="10"/>
+      <c r="I10" s="6"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -2224,7 +2735,7 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="Q10" s="10"/>
+      <c r="Q10" s="6"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -2242,23 +2753,23 @@
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
-      <c r="AI10" s="9"/>
+      <c r="AI10" s="2"/>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
     </row>
-    <row r="11" spans="1:40" ht="18" customHeight="1">
-      <c r="A11" s="9"/>
+    <row r="11" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="9"/>
+      <c r="D11" s="2"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="10"/>
+      <c r="I11" s="6"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -2266,7 +2777,7 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="10"/>
+      <c r="Q11" s="6"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
@@ -2284,23 +2795,23 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-      <c r="AI11" s="9"/>
+      <c r="AI11" s="2"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:40" ht="18" customHeight="1">
-      <c r="A12" s="9"/>
+    <row r="12" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="9"/>
+      <c r="D12" s="2"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="10"/>
+      <c r="I12" s="6"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -2308,7 +2819,7 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="10"/>
+      <c r="Q12" s="6"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -2326,23 +2837,23 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
-      <c r="AI12" s="9"/>
+      <c r="AI12" s="2"/>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
-    <row r="13" spans="1:40" ht="18" customHeight="1">
-      <c r="A13" s="9"/>
+    <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="9"/>
+      <c r="D13" s="2"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="10"/>
+      <c r="I13" s="6"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -2350,7 +2861,7 @@
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-      <c r="Q13" s="10"/>
+      <c r="Q13" s="6"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
@@ -2368,23 +2879,23 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
-      <c r="AI13" s="9"/>
+      <c r="AI13" s="2"/>
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
     </row>
-    <row r="14" spans="1:40" ht="18" customHeight="1">
-      <c r="A14" s="9"/>
+    <row r="14" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="9"/>
+      <c r="D14" s="2"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="10"/>
+      <c r="I14" s="6"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -2392,7 +2903,7 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-      <c r="Q14" s="10"/>
+      <c r="Q14" s="6"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -2410,7 +2921,7 @@
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
-      <c r="AI14" s="9"/>
+      <c r="AI14" s="2"/>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
@@ -2419,40 +2930,8 @@
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="AI14:AN14"/>
-    <mergeCell ref="AI13:AN13"/>
-    <mergeCell ref="I8:P8"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="Q13:AH13"/>
-    <mergeCell ref="AI10:AN10"/>
-    <mergeCell ref="AI6:AN6"/>
-    <mergeCell ref="I6:P6"/>
-    <mergeCell ref="Q5:AH5"/>
-    <mergeCell ref="AI9:AN9"/>
-    <mergeCell ref="AI12:AN12"/>
-    <mergeCell ref="AI5:AN5"/>
-    <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="AI11:AN11"/>
-    <mergeCell ref="Q10:AH10"/>
-    <mergeCell ref="I11:P11"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="AI7:AN7"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="Q6:AH6"/>
-    <mergeCell ref="I7:P7"/>
-    <mergeCell ref="AA2:AD2"/>
-    <mergeCell ref="AI4:AN4"/>
-    <mergeCell ref="I14:P14"/>
-    <mergeCell ref="I9:P9"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="Q4:AH4"/>
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="Q14:AH14"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="I12:P12"/>
@@ -2469,6 +2948,12 @@
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="D14:H14"/>
     <mergeCell ref="I13:P13"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="Q4:AH4"/>
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="AA1:AD1"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="Q8:AH8"/>
     <mergeCell ref="AE1:AN1"/>
@@ -2479,10 +2964,36 @@
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="Q12:AH12"/>
     <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="Q6:AH6"/>
+    <mergeCell ref="I7:P7"/>
+    <mergeCell ref="AA2:AD2"/>
     <mergeCell ref="D5:H5"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="AI11:AN11"/>
+    <mergeCell ref="Q10:AH10"/>
+    <mergeCell ref="I11:P11"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="I9:P9"/>
     <mergeCell ref="I10:P10"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="AI14:AN14"/>
+    <mergeCell ref="AI13:AN13"/>
+    <mergeCell ref="I8:P8"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="Q13:AH13"/>
+    <mergeCell ref="AI10:AN10"/>
+    <mergeCell ref="AI6:AN6"/>
+    <mergeCell ref="I6:P6"/>
+    <mergeCell ref="Q5:AH5"/>
+    <mergeCell ref="AI9:AN9"/>
+    <mergeCell ref="AI12:AN12"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="AI7:AN7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="I14:P14"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -2496,13 +3007,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN14"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="3"/>
@@ -2512,13 +3023,13 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="13" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -2534,13 +3045,13 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="9" t="s">
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -2553,7 +3064,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2562,13 +3073,13 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -2584,13 +3095,13 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="9"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -2601,18 +3112,18 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="4" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="13" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="3"/>
@@ -2647,18 +3158,18 @@
       <c r="AM4" s="3"/>
       <c r="AN4" s="3"/>
     </row>
-    <row r="5" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="11" t="s">
+    <row r="5" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="13" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="7" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="3"/>
@@ -2693,18 +3204,18 @@
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
-    <row r="6" spans="1:40" ht="30" customHeight="1">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="13" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="7" t="s">
         <v>24</v>
       </c>
       <c r="J6" s="3"/>
@@ -2739,18 +3250,18 @@
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
     </row>
-    <row r="7" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="13" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="7" t="s">
         <v>26</v>
       </c>
       <c r="J7" s="3"/>
@@ -2785,19 +3296,19 @@
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
     </row>
-    <row r="8" spans="1:40" ht="30" customHeight="1">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="13" t="s">
-        <v>178</v>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -2831,18 +3342,18 @@
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
-    <row r="9" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="13" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="7" t="s">
         <v>29</v>
       </c>
       <c r="J9" s="3"/>
@@ -2877,18 +3388,18 @@
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
     </row>
-    <row r="10" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="13" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="7" t="s">
         <v>29</v>
       </c>
       <c r="J10" s="3"/>
@@ -2923,18 +3434,18 @@
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
     </row>
-    <row r="11" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="13" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="7" t="s">
         <v>32</v>
       </c>
       <c r="J11" s="3"/>
@@ -2969,18 +3480,18 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="13" t="s">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="7" t="s">
         <v>34</v>
       </c>
       <c r="J12" s="3"/>
@@ -3015,18 +3526,18 @@
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
-    <row r="13" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="11" t="s">
+    <row r="13" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="13" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="7" t="s">
         <v>36</v>
       </c>
       <c r="J13" s="3"/>
@@ -3061,18 +3572,18 @@
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
     </row>
-    <row r="14" spans="1:40" ht="30" customHeight="1">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="13" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="7" t="s">
         <v>38</v>
       </c>
       <c r="J14" s="3"/>
@@ -3109,6 +3620,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="I12:AN12"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="I5:AN5"/>
+    <mergeCell ref="I14:AN14"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="I8:AN8"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="I4:AN4"/>
+    <mergeCell ref="AE1:AN1"/>
+    <mergeCell ref="A9:H9"/>
     <mergeCell ref="I10:AN10"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="I13:AN13"/>
@@ -3125,21 +3651,6 @@
     <mergeCell ref="AA1:AD1"/>
     <mergeCell ref="I7:AN7"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="I12:AN12"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="I5:AN5"/>
-    <mergeCell ref="I14:AN14"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="I8:AN8"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="I4:AN4"/>
-    <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="A9:H9"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3153,13 +3664,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN24"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="3"/>
@@ -3169,13 +3680,13 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="13" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -3191,13 +3702,13 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="9" t="s">
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -3210,7 +3721,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3219,13 +3730,13 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -3241,13 +3752,13 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="9"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -3258,7 +3769,7 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="24" spans="1:1" ht="14.25">
+    <row r="24" spans="1:1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>40</v>
       </c>
@@ -3288,13 +3799,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN17"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B1" s="3"/>
@@ -3304,13 +3815,13 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="13" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -3326,13 +3837,13 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="9" t="s">
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -3345,7 +3856,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3354,13 +3865,13 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -3376,13 +3887,13 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="9"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -3393,79 +3904,79 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="4" spans="1:40">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="11" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="11" t="s">
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="11" t="s">
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="T4" s="6"/>
-      <c r="U4" s="11" t="s">
+      <c r="T4" s="5"/>
+      <c r="U4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="V4" s="6"/>
-      <c r="W4" s="11" t="s">
+      <c r="V4" s="5"/>
+      <c r="W4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="11" t="s">
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="11" t="s">
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-    </row>
-    <row r="5" spans="1:40" ht="27.95" customHeight="1">
-      <c r="A5" s="9">
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+    </row>
+    <row r="5" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I5" s="3"/>
@@ -3474,34 +3985,34 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="9" t="s">
+      <c r="O5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="S5" s="9" t="s">
+      <c r="S5" s="2" t="s">
         <v>53</v>
       </c>
       <c r="T5" s="3"/>
-      <c r="U5" s="9" t="s">
+      <c r="U5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="V5" s="3"/>
-      <c r="W5" s="10" t="s">
+      <c r="W5" s="6" t="s">
         <v>51</v>
       </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
-      <c r="AB5" s="10" t="s">
+      <c r="AB5" s="6" t="s">
         <v>54</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
-      <c r="AF5" s="10" t="s">
+      <c r="AF5" s="6" t="s">
         <v>55</v>
       </c>
       <c r="AG5" s="3"/>
@@ -3513,19 +4024,19 @@
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
-    <row r="6" spans="1:40" ht="18" customHeight="1">
-      <c r="A6" s="9">
+    <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="6" t="s">
         <v>56</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I6" s="3"/>
@@ -3534,34 +4045,34 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-      <c r="S6" s="9" t="s">
+      <c r="S6" s="2" t="s">
         <v>53</v>
       </c>
       <c r="T6" s="3"/>
-      <c r="U6" s="9" t="s">
+      <c r="U6" s="2" t="s">
         <v>51</v>
       </c>
       <c r="V6" s="3"/>
-      <c r="W6" s="10" t="s">
+      <c r="W6" s="6" t="s">
         <v>51</v>
       </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
-      <c r="AB6" s="10" t="s">
+      <c r="AB6" s="6" t="s">
         <v>58</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
-      <c r="AF6" s="10"/>
+      <c r="AF6" s="6"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
@@ -3571,19 +4082,19 @@
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
     </row>
-    <row r="7" spans="1:40" ht="18" customHeight="1">
-      <c r="A7" s="9">
+    <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>59</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="6" t="s">
         <v>60</v>
       </c>
       <c r="I7" s="3"/>
@@ -3592,34 +4103,34 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="9" t="s">
+      <c r="O7" s="2" t="s">
         <v>61</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-      <c r="S7" s="9" t="s">
+      <c r="S7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T7" s="3"/>
-      <c r="U7" s="9" t="s">
+      <c r="U7" s="2" t="s">
         <v>63</v>
       </c>
       <c r="V7" s="3"/>
-      <c r="W7" s="10" t="s">
+      <c r="W7" s="6" t="s">
         <v>64</v>
       </c>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
-      <c r="AB7" s="10" t="s">
+      <c r="AB7" s="6" t="s">
         <v>65</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
-      <c r="AF7" s="10" t="s">
+      <c r="AF7" s="6" t="s">
         <v>66</v>
       </c>
       <c r="AG7" s="3"/>
@@ -3631,19 +4142,19 @@
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
     </row>
-    <row r="8" spans="1:40" ht="18" customHeight="1">
-      <c r="A8" s="9">
+    <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="6" t="s">
         <v>67</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="6" t="s">
         <v>60</v>
       </c>
       <c r="I8" s="3"/>
@@ -3652,34 +4163,34 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="9" t="s">
+      <c r="O8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="S8" s="9" t="s">
+      <c r="S8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T8" s="3"/>
-      <c r="U8" s="9" t="s">
+      <c r="U8" s="2" t="s">
         <v>63</v>
       </c>
       <c r="V8" s="3"/>
-      <c r="W8" s="10" t="s">
+      <c r="W8" s="6" t="s">
         <v>68</v>
       </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
-      <c r="AB8" s="10" t="s">
+      <c r="AB8" s="6" t="s">
         <v>69</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
-      <c r="AF8" s="10" t="s">
+      <c r="AF8" s="6" t="s">
         <v>70</v>
       </c>
       <c r="AG8" s="3"/>
@@ -3691,19 +4202,19 @@
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
-    <row r="9" spans="1:40" ht="27.95" customHeight="1">
-      <c r="A9" s="9">
+    <row r="9" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="6" t="s">
         <v>72</v>
       </c>
       <c r="I9" s="3"/>
@@ -3712,35 +4223,35 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="9" t="s">
-        <v>172</v>
+      <c r="O9" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="S9" s="9" t="s">
+      <c r="S9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T9" s="3"/>
-      <c r="U9" s="9" t="s">
+      <c r="U9" s="2" t="s">
         <v>63</v>
       </c>
       <c r="V9" s="3"/>
-      <c r="W9" s="10" t="s">
-        <v>173</v>
+      <c r="W9" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
-      <c r="AB9" s="10" t="s">
-        <v>174</v>
+      <c r="AB9" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
-      <c r="AF9" s="10" t="s">
-        <v>175</v>
+      <c r="AF9" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -3751,19 +4262,19 @@
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
     </row>
-    <row r="10" spans="1:40" ht="27.95" customHeight="1">
-      <c r="A10" s="9">
+    <row r="10" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
         <v>6</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="6" t="s">
         <v>75</v>
       </c>
       <c r="I10" s="3"/>
@@ -3772,35 +4283,35 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="9" t="s">
-        <v>172</v>
+      <c r="O10" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="9" t="s">
+      <c r="S10" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T10" s="3"/>
-      <c r="U10" s="9" t="s">
+      <c r="U10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="V10" s="3"/>
-      <c r="W10" s="10" t="s">
-        <v>173</v>
+      <c r="W10" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
-      <c r="AB10" s="10" t="s">
-        <v>174</v>
+      <c r="AB10" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
-      <c r="AF10" s="10" t="s">
-        <v>176</v>
+      <c r="AF10" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
@@ -3811,19 +4322,19 @@
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
     </row>
-    <row r="11" spans="1:40" ht="18" customHeight="1">
-      <c r="A11" s="9">
+    <row r="11" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="6" t="s">
         <v>77</v>
       </c>
       <c r="I11" s="3"/>
@@ -3832,34 +4343,34 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="9" t="s">
+      <c r="O11" s="2" t="s">
         <v>78</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="9" t="s">
+      <c r="S11" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T11" s="3"/>
-      <c r="U11" s="9" t="s">
+      <c r="U11" s="2" t="s">
         <v>63</v>
       </c>
       <c r="V11" s="3"/>
-      <c r="W11" s="10" t="s">
+      <c r="W11" s="6" t="s">
         <v>79</v>
       </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-      <c r="AB11" s="10" t="s">
+      <c r="AB11" s="6" t="s">
         <v>73</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-      <c r="AF11" s="10"/>
+      <c r="AF11" s="6"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
@@ -3869,19 +4380,19 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:40" ht="27.95" customHeight="1">
-      <c r="A12" s="9">
+    <row r="12" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="6" t="s">
         <v>81</v>
       </c>
       <c r="I12" s="3"/>
@@ -3890,34 +4401,34 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="2" t="s">
         <v>78</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="9" t="s">
+      <c r="S12" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T12" s="3"/>
-      <c r="U12" s="9" t="s">
+      <c r="U12" s="2" t="s">
         <v>82</v>
       </c>
       <c r="V12" s="3"/>
-      <c r="W12" s="10" t="s">
+      <c r="W12" s="6" t="s">
         <v>79</v>
       </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
-      <c r="AB12" s="10" t="s">
+      <c r="AB12" s="6" t="s">
         <v>73</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
-      <c r="AF12" s="10" t="s">
+      <c r="AF12" s="6" t="s">
         <v>83</v>
       </c>
       <c r="AG12" s="3"/>
@@ -3929,19 +4440,19 @@
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
-    <row r="13" spans="1:40" ht="27.95" customHeight="1">
-      <c r="A13" s="9">
+    <row r="13" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="6" t="s">
         <v>85</v>
       </c>
       <c r="I13" s="3"/>
@@ -3950,34 +4461,34 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="2" t="s">
         <v>86</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="9" t="s">
+      <c r="S13" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T13" s="3"/>
-      <c r="U13" s="9" t="s">
+      <c r="U13" s="2" t="s">
         <v>63</v>
       </c>
       <c r="V13" s="3"/>
-      <c r="W13" s="10" t="s">
+      <c r="W13" s="6" t="s">
         <v>87</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
-      <c r="AB13" s="10" t="s">
+      <c r="AB13" s="6" t="s">
         <v>88</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
-      <c r="AF13" s="10" t="s">
+      <c r="AF13" s="6" t="s">
         <v>89</v>
       </c>
       <c r="AG13" s="3"/>
@@ -3989,19 +4500,19 @@
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
     </row>
-    <row r="14" spans="1:40" ht="27.95" customHeight="1">
-      <c r="A14" s="9">
+    <row r="14" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="6" t="s">
         <v>90</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="6" t="s">
         <v>91</v>
       </c>
       <c r="I14" s="3"/>
@@ -4010,34 +4521,34 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="9" t="s">
+      <c r="O14" s="2" t="s">
         <v>86</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-      <c r="S14" s="9" t="s">
+      <c r="S14" s="2" t="s">
         <v>62</v>
       </c>
       <c r="T14" s="3"/>
-      <c r="U14" s="9" t="s">
+      <c r="U14" s="2" t="s">
         <v>63</v>
       </c>
       <c r="V14" s="3"/>
-      <c r="W14" s="10" t="s">
+      <c r="W14" s="6" t="s">
         <v>92</v>
       </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
-      <c r="AB14" s="10" t="s">
+      <c r="AB14" s="6" t="s">
         <v>93</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
-      <c r="AF14" s="10" t="s">
+      <c r="AF14" s="6" t="s">
         <v>89</v>
       </c>
       <c r="AG14" s="3"/>
@@ -4049,19 +4560,19 @@
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
     </row>
-    <row r="15" spans="1:40" ht="18" customHeight="1">
-      <c r="A15" s="9">
+    <row r="15" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
         <v>11</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="6" t="s">
         <v>94</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="6" t="s">
         <v>51</v>
       </c>
       <c r="I15" s="3"/>
@@ -4070,35 +4581,35 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="9" t="s">
+      <c r="O15" s="2" t="s">
         <v>95</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="9" t="s">
+      <c r="S15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="T15" s="3"/>
-      <c r="U15" s="9" t="s">
+      <c r="U15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="V15" s="3"/>
-      <c r="W15" s="10" t="s">
+      <c r="W15" s="6" t="s">
         <v>51</v>
       </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
-      <c r="AB15" s="10" t="s">
+      <c r="AB15" s="6" t="s">
         <v>51</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
-      <c r="AF15" s="10" t="s">
-        <v>177</v>
+      <c r="AF15" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
@@ -4109,13 +4620,106 @@
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
     </row>
-    <row r="17" spans="1:1" ht="14.25">
+    <row r="17" spans="1:1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="117">
+    <mergeCell ref="AE1:AN1"/>
+    <mergeCell ref="W13:AA13"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="W6:AA6"/>
+    <mergeCell ref="W15:AA15"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="S8:T8"/>
+    <mergeCell ref="H8:N8"/>
+    <mergeCell ref="S11:T11"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="AB6:AE6"/>
+    <mergeCell ref="O10:R10"/>
+    <mergeCell ref="AB15:AE15"/>
+    <mergeCell ref="H10:N10"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="AF7:AN7"/>
+    <mergeCell ref="H9:N9"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="W11:AA11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="O5:R5"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="W9:AA9"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="AB9:AE9"/>
+    <mergeCell ref="W14:AA14"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="AB11:AE11"/>
+    <mergeCell ref="AF14:AN14"/>
+    <mergeCell ref="AB7:AE7"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="O11:R11"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="H11:N11"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="AB8:AE8"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="AF11:AN11"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="W12:AA12"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="AB12:AE12"/>
+    <mergeCell ref="H7:N7"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="AF4:AN4"/>
+    <mergeCell ref="W4:AA4"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="AF10:AN10"/>
+    <mergeCell ref="W10:AA10"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="AF5:AN5"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="AF8:AN8"/>
+    <mergeCell ref="AF6:AN6"/>
+    <mergeCell ref="AF9:AN9"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O9:R9"/>
+    <mergeCell ref="H4:N4"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="AF15:AN15"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="AF12:AN12"/>
+    <mergeCell ref="O13:R13"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="O7:R7"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="AB5:AE5"/>
+    <mergeCell ref="O15:R15"/>
+    <mergeCell ref="AB14:AE14"/>
+    <mergeCell ref="W7:AA7"/>
+    <mergeCell ref="S10:T10"/>
+    <mergeCell ref="AB4:AE4"/>
+    <mergeCell ref="AF13:AN13"/>
+    <mergeCell ref="S9:T9"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="W8:AA8"/>
+    <mergeCell ref="H6:N6"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="O12:R12"/>
@@ -4140,99 +4744,6 @@
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C11:G11"/>
     <mergeCell ref="AA2:AD2"/>
-    <mergeCell ref="AF9:AN9"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O9:R9"/>
-    <mergeCell ref="H4:N4"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="AF15:AN15"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="AF12:AN12"/>
-    <mergeCell ref="O13:R13"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="O7:R7"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="AB5:AE5"/>
-    <mergeCell ref="O15:R15"/>
-    <mergeCell ref="AB14:AE14"/>
-    <mergeCell ref="W7:AA7"/>
-    <mergeCell ref="S10:T10"/>
-    <mergeCell ref="AB4:AE4"/>
-    <mergeCell ref="AF13:AN13"/>
-    <mergeCell ref="S9:T9"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="W8:AA8"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="AF11:AN11"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="W12:AA12"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="AB12:AE12"/>
-    <mergeCell ref="H7:N7"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="AF4:AN4"/>
-    <mergeCell ref="W4:AA4"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="AF10:AN10"/>
-    <mergeCell ref="W10:AA10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="AF5:AN5"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="AF8:AN8"/>
-    <mergeCell ref="AF6:AN6"/>
-    <mergeCell ref="H6:N6"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="W9:AA9"/>
-    <mergeCell ref="O4:R4"/>
-    <mergeCell ref="AB9:AE9"/>
-    <mergeCell ref="W14:AA14"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="AB11:AE11"/>
-    <mergeCell ref="AF14:AN14"/>
-    <mergeCell ref="AB7:AE7"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="O11:R11"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="H11:N11"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AB8:AE8"/>
-    <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="W13:AA13"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="W6:AA6"/>
-    <mergeCell ref="W15:AA15"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="S8:T8"/>
-    <mergeCell ref="H8:N8"/>
-    <mergeCell ref="S11:T11"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="AB6:AE6"/>
-    <mergeCell ref="O10:R10"/>
-    <mergeCell ref="AB15:AE15"/>
-    <mergeCell ref="H10:N10"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="AF7:AN7"/>
-    <mergeCell ref="H9:N9"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="W11:AA11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="O5:R5"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4246,13 +4757,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
         <v>97</v>
       </c>
       <c r="B1" s="3"/>
@@ -4262,13 +4773,13 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="13" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -4284,13 +4795,13 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="9" t="s">
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -4303,7 +4814,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -4312,13 +4823,13 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -4334,13 +4845,13 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="9"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -4351,64 +4862,64 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="4" spans="1:40">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="11" t="s">
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="11" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="11" t="s">
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="5"/>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-    </row>
-    <row r="5" spans="1:40" ht="84" customHeight="1">
-      <c r="A5" s="9">
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+    </row>
+    <row r="5" spans="1:40" ht="84" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>101</v>
       </c>
       <c r="D5" s="3"/>
@@ -4416,7 +4927,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="6" t="s">
         <v>102</v>
       </c>
       <c r="J5" s="3"/>
@@ -4424,8 +4935,8 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="10" t="s">
-        <v>169</v>
+      <c r="O5" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
@@ -4446,7 +4957,7 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
-      <c r="AI5" s="9" t="s">
+      <c r="AI5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="AJ5" s="3"/>
@@ -4455,341 +4966,341 @@
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
-    <row r="6" spans="1:40" ht="18" customHeight="1">
-      <c r="A6" s="9">
+    <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="28">
         <v>2</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="29"/>
+      <c r="C6" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="10" t="s">
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="10" t="s">
+      <c r="J6" s="29"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="9" t="s">
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="3"/>
-    </row>
-    <row r="7" spans="1:40" ht="18" customHeight="1">
-      <c r="A7" s="9">
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+    </row>
+    <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="28">
         <v>3</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="29"/>
+      <c r="C7" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="10" t="s">
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="10" t="s">
+      <c r="J7" s="29"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
-      <c r="AG7" s="3"/>
-      <c r="AH7" s="3"/>
-      <c r="AI7" s="9" t="s">
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="29"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="29"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="29"/>
+      <c r="AI7" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="AJ7" s="3"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="3"/>
-      <c r="AM7" s="3"/>
-      <c r="AN7" s="3"/>
-    </row>
-    <row r="8" spans="1:40" ht="36" customHeight="1">
-      <c r="A8" s="9">
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="29"/>
+      <c r="AL7" s="29"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+    </row>
+    <row r="8" spans="1:40" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="28">
         <v>4</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="29"/>
+      <c r="C8" s="30" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="29"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="10" t="s">
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="29"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="29"/>
+      <c r="AI8" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="29"/>
+      <c r="AL8" s="29"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="29"/>
+    </row>
+    <row r="9" spans="1:40" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="28">
+        <v>5</v>
+      </c>
+      <c r="B9" s="29"/>
+      <c r="C9" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="3"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="9" t="s">
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="J9" s="29"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="29"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="30" t="s">
+        <v>167</v>
+      </c>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="29"/>
+      <c r="W9" s="29"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="29"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="29"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="29"/>
+      <c r="AI9" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="AJ8" s="3"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="3"/>
-      <c r="AN8" s="3"/>
-    </row>
-    <row r="9" spans="1:40" ht="36" customHeight="1">
-      <c r="A9" s="9">
-        <v>5</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="3"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="9" t="s">
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="29"/>
+      <c r="AL9" s="29"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="29"/>
+    </row>
+    <row r="10" spans="1:40" ht="84" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="28">
+        <v>6</v>
+      </c>
+      <c r="B10" s="29"/>
+      <c r="C10" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="29"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="30" t="s">
+        <v>110</v>
+      </c>
+      <c r="J10" s="29"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="29"/>
+      <c r="W10" s="29"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="29"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="29"/>
+      <c r="AF10" s="29"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="29"/>
+      <c r="AI10" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="3"/>
-      <c r="AN9" s="3"/>
-    </row>
-    <row r="10" spans="1:40" ht="84" customHeight="1">
-      <c r="A10" s="9">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="10" t="s">
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="29"/>
+      <c r="AL10" s="29"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="29"/>
+    </row>
+    <row r="11" spans="1:40" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="28">
+        <v>7</v>
+      </c>
+      <c r="B11" s="29"/>
+      <c r="C11" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
-      <c r="AG10" s="3"/>
-      <c r="AH10" s="3"/>
-      <c r="AI10" s="9" t="s">
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="29"/>
+      <c r="W11" s="29"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="29"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="29"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="29"/>
+      <c r="AI11" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="AJ10" s="3"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="3"/>
-      <c r="AN10" s="3"/>
-    </row>
-    <row r="11" spans="1:40" ht="69.95" customHeight="1">
-      <c r="A11" s="9">
-        <v>7</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="10" t="s">
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="29"/>
+      <c r="AL11" s="29"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="29"/>
+    </row>
+    <row r="12" spans="1:40" ht="140.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="3"/>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-    </row>
-    <row r="12" spans="1:40" ht="140.1" customHeight="1">
-      <c r="A12" s="9">
-        <v>8</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="10" t="s">
-        <v>114</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="10" t="s">
-        <v>115</v>
+      <c r="I12" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="10" t="s">
-        <v>171</v>
+      <c r="O12" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -4810,8 +5321,8 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
-      <c r="AI12" s="9" t="s">
-        <v>116</v>
+      <c r="AI12" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
@@ -4819,29 +5330,29 @@
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
-    <row r="13" spans="1:40" ht="18" customHeight="1">
-      <c r="A13" s="9">
+    <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="10" t="s">
-        <v>117</v>
+      <c r="C13" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="10" t="s">
-        <v>118</v>
+      <c r="I13" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="10" t="s">
-        <v>119</v>
+      <c r="O13" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -4862,7 +5373,7 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
-      <c r="AI13" s="9" t="s">
+      <c r="AI13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="AJ13" s="3"/>
@@ -4873,17 +5384,38 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="O7:AH7"/>
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="O5:AH5"/>
-    <mergeCell ref="I4:N4"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="O4:AH4"/>
-    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="AI12:AN12"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="O10:AH10"/>
+    <mergeCell ref="O13:AH13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="AI11:AN11"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="O8:AH8"/>
+    <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="I11:N11"/>
+    <mergeCell ref="AI10:AN10"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="AE1:AN1"/>
+    <mergeCell ref="O9:AH9"/>
+    <mergeCell ref="AI9:AN9"/>
+    <mergeCell ref="I7:N7"/>
+    <mergeCell ref="AI6:AN6"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C11:H11"/>
     <mergeCell ref="AI13:AN13"/>
@@ -4900,38 +5432,17 @@
     <mergeCell ref="M2:Z2"/>
     <mergeCell ref="C10:H10"/>
     <mergeCell ref="I10:N10"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="AI5:AN5"/>
-    <mergeCell ref="I11:N11"/>
-    <mergeCell ref="AI10:AN10"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="I6:N6"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="O9:AH9"/>
-    <mergeCell ref="AI9:AN9"/>
-    <mergeCell ref="I7:N7"/>
-    <mergeCell ref="AI6:AN6"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="AI12:AN12"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="O10:AH10"/>
-    <mergeCell ref="O13:AH13"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="AI11:AN11"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="O8:AH8"/>
-    <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="O7:AH7"/>
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="O5:AH5"/>
+    <mergeCell ref="I4:N4"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="O4:AH4"/>
+    <mergeCell ref="I12:N12"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4945,14 +5456,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN8"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>188</v>
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4961,13 +5472,13 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="13" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -4983,13 +5494,13 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="9" t="s">
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -5002,7 +5513,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5011,13 +5522,13 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -5033,13 +5544,13 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="9"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -5050,210 +5561,211 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="4" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="27"/>
+      <c r="C4" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="17" t="s">
+      <c r="K4" s="25"/>
+      <c r="L4" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="K4" s="19"/>
-      <c r="L4" s="17" t="s">
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="25"/>
+      <c r="Q4" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
-      <c r="O4" s="18"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="17" t="s">
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="25"/>
+      <c r="U4" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="R4" s="18"/>
-      <c r="S4" s="18"/>
-      <c r="T4" s="19"/>
-      <c r="U4" s="17" t="s">
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="25"/>
+      <c r="AA4" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="V4" s="18"/>
-      <c r="W4" s="18"/>
-      <c r="X4" s="18"/>
-      <c r="Y4" s="18"/>
-      <c r="Z4" s="19"/>
-      <c r="AA4" s="17" t="s">
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="25"/>
+      <c r="AF4" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="AB4" s="18"/>
-      <c r="AC4" s="18"/>
-      <c r="AD4" s="18"/>
-      <c r="AE4" s="19"/>
-      <c r="AF4" s="17" t="s">
+      <c r="AG4" s="24"/>
+      <c r="AH4" s="24"/>
+      <c r="AI4" s="24"/>
+      <c r="AJ4" s="25"/>
+      <c r="AK4" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="AG4" s="18"/>
-      <c r="AH4" s="18"/>
-      <c r="AI4" s="18"/>
-      <c r="AJ4" s="19"/>
-      <c r="AK4" s="17" t="s">
+      <c r="AL4" s="24"/>
+      <c r="AM4" s="24"/>
+      <c r="AN4" s="25"/>
+    </row>
+    <row r="5" spans="1:40" ht="62.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="18">
+        <v>1</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="18" t="s">
         <v>197</v>
       </c>
-      <c r="AL4" s="18"/>
-      <c r="AM4" s="18"/>
-      <c r="AN4" s="19"/>
-    </row>
-    <row r="5" spans="1:40" ht="62.1" customHeight="1">
-      <c r="A5" s="20">
-        <v>1</v>
-      </c>
-      <c r="B5" s="21"/>
-      <c r="C5" s="20" t="s">
+      <c r="D5" s="19"/>
+      <c r="E5" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22" t="s">
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="20" t="s">
         <v>199</v>
       </c>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="22" t="s">
+      <c r="K5" s="22"/>
+      <c r="L5" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="K5" s="24"/>
-      <c r="L5" s="25" t="s">
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="17"/>
+      <c r="Q5" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="M5" s="26"/>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="25" t="s">
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="17"/>
+      <c r="U5" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="R5" s="26"/>
-      <c r="S5" s="26"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="25" t="s">
+      <c r="V5" s="16"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="16"/>
+      <c r="Z5" s="17"/>
+      <c r="AA5" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="V5" s="26"/>
-      <c r="W5" s="26"/>
-      <c r="X5" s="26"/>
-      <c r="Y5" s="26"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="25" t="s">
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="16"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="17"/>
+      <c r="AF5" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AB5" s="26"/>
-      <c r="AC5" s="26"/>
-      <c r="AD5" s="26"/>
-      <c r="AE5" s="27"/>
-      <c r="AF5" s="25" t="s">
+      <c r="AG5" s="16"/>
+      <c r="AH5" s="16"/>
+      <c r="AI5" s="16"/>
+      <c r="AJ5" s="17"/>
+      <c r="AK5" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="AG5" s="26"/>
-      <c r="AH5" s="26"/>
-      <c r="AI5" s="26"/>
-      <c r="AJ5" s="27"/>
-      <c r="AK5" s="25" t="s">
+      <c r="AL5" s="16"/>
+      <c r="AM5" s="16"/>
+      <c r="AN5" s="17"/>
+    </row>
+    <row r="6" spans="1:40" ht="104.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="18">
+        <v>2</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="19"/>
+      <c r="E6" s="20" t="s">
         <v>206</v>
       </c>
-      <c r="AL5" s="26"/>
-      <c r="AM5" s="26"/>
-      <c r="AN5" s="27"/>
-    </row>
-    <row r="6" spans="1:40" ht="104.1" customHeight="1">
-      <c r="A6" s="20">
-        <v>2</v>
-      </c>
-      <c r="B6" s="21"/>
-      <c r="C6" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="22" t="s">
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="K6" s="22"/>
+      <c r="L6" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="K6" s="24"/>
-      <c r="L6" s="25" t="s">
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="26"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="25" t="s">
+      <c r="R6" s="16"/>
+      <c r="S6" s="16"/>
+      <c r="T6" s="17"/>
+      <c r="U6" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="R6" s="26"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="25" t="s">
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="16"/>
+      <c r="Z6" s="17"/>
+      <c r="AA6" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="V6" s="26"/>
-      <c r="W6" s="26"/>
-      <c r="X6" s="26"/>
-      <c r="Y6" s="26"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="25" t="s">
+      <c r="AB6" s="16"/>
+      <c r="AC6" s="16"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="17"/>
+      <c r="AF6" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="AB6" s="26"/>
-      <c r="AC6" s="26"/>
-      <c r="AD6" s="26"/>
-      <c r="AE6" s="27"/>
-      <c r="AF6" s="25" t="s">
+      <c r="AG6" s="16"/>
+      <c r="AH6" s="16"/>
+      <c r="AI6" s="16"/>
+      <c r="AJ6" s="17"/>
+      <c r="AK6" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="AG6" s="26"/>
-      <c r="AH6" s="26"/>
-      <c r="AI6" s="26"/>
-      <c r="AJ6" s="27"/>
-      <c r="AK6" s="25" t="s">
+      <c r="AL6" s="16"/>
+      <c r="AM6" s="16"/>
+      <c r="AN6" s="17"/>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
         <v>213</v>
-      </c>
-      <c r="AL6" s="26"/>
-      <c r="AM6" s="26"/>
-      <c r="AN6" s="27"/>
-    </row>
-    <row r="8" spans="1:40">
-      <c r="A8" t="s">
-        <v>214</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="AK6:AN6"/>
-    <mergeCell ref="AF5:AJ5"/>
-    <mergeCell ref="AK5:AN5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="L6:P6"/>
-    <mergeCell ref="Q6:T6"/>
-    <mergeCell ref="U6:Z6"/>
-    <mergeCell ref="AA6:AE6"/>
-    <mergeCell ref="AF6:AJ6"/>
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="AE1:AN1"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="AA2:AD2"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:L1"/>
     <mergeCell ref="AA4:AE4"/>
     <mergeCell ref="AF4:AJ4"/>
     <mergeCell ref="AK4:AN4"/>
@@ -5270,18 +5782,17 @@
     <mergeCell ref="L4:P4"/>
     <mergeCell ref="Q4:T4"/>
     <mergeCell ref="U4:Z4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="AA2:AD2"/>
-    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="AK6:AN6"/>
+    <mergeCell ref="AF5:AJ5"/>
+    <mergeCell ref="AK5:AN5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="U6:Z6"/>
+    <mergeCell ref="AA6:AE6"/>
+    <mergeCell ref="AF6:AJ6"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -5295,14 +5806,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN18"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>120</v>
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
+        <v>119</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5311,13 +5822,13 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="13" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -5333,13 +5844,13 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="9" t="s">
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -5352,7 +5863,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5361,13 +5872,13 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -5383,13 +5894,13 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="9"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -5400,68 +5911,68 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="4" spans="1:40">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="11" t="s">
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="11" t="s">
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="11" t="s">
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-    </row>
-    <row r="5" spans="1:40" ht="18" customHeight="1">
-      <c r="A5" s="9">
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+    </row>
+    <row r="5" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
         <v>1</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="3"/>
@@ -5469,8 +5980,8 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="10" t="s">
-        <v>126</v>
+      <c r="I5" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -5487,35 +5998,35 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
-      <c r="Y5" s="9" t="s">
+      <c r="Y5" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
-      <c r="AC5" s="9" t="s">
+      <c r="AC5" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
-      <c r="AG5" s="9" t="s">
-        <v>127</v>
+      <c r="AG5" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
-      <c r="AK5" s="10"/>
+      <c r="AK5" s="6"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
-    <row r="6" spans="1:40" ht="18" customHeight="1">
-      <c r="A6" s="9">
+    <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D6" s="3"/>
@@ -5523,8 +6034,8 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="10" t="s">
-        <v>128</v>
+      <c r="I6" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -5541,35 +6052,35 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
-      <c r="Y6" s="9" t="s">
+      <c r="Y6" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
-      <c r="AC6" s="9" t="s">
+      <c r="AC6" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
-      <c r="AG6" s="9" t="s">
-        <v>129</v>
+      <c r="AG6" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
-      <c r="AK6" s="10"/>
+      <c r="AK6" s="6"/>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
     </row>
-    <row r="7" spans="1:40" ht="18" customHeight="1">
-      <c r="A7" s="9">
+    <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
         <v>3</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="3"/>
@@ -5577,8 +6088,8 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="10" t="s">
-        <v>126</v>
+      <c r="I7" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -5595,35 +6106,35 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
-      <c r="Y7" s="9" t="s">
+      <c r="Y7" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
-      <c r="AC7" s="9" t="s">
+      <c r="AC7" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
-      <c r="AG7" s="9" t="s">
-        <v>127</v>
+      <c r="AG7" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
-      <c r="AK7" s="10"/>
+      <c r="AK7" s="6"/>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
     </row>
-    <row r="8" spans="1:40" ht="18" customHeight="1">
-      <c r="A8" s="9">
+    <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="3"/>
@@ -5631,8 +6142,8 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="10" t="s">
-        <v>128</v>
+      <c r="I8" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -5649,44 +6160,44 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
-      <c r="Y8" s="9" t="s">
+      <c r="Y8" s="2" t="s">
         <v>51</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
-      <c r="AC8" s="9" t="s">
+      <c r="AC8" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
-      <c r="AG8" s="9" t="s">
-        <v>129</v>
+      <c r="AG8" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
-      <c r="AK8" s="10"/>
+      <c r="AK8" s="6"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
-    <row r="9" spans="1:40" ht="18" customHeight="1">
-      <c r="A9" s="9">
+    <row r="9" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
         <v>5</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="10" t="s">
-        <v>130</v>
+      <c r="C9" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="10" t="s">
-        <v>131</v>
+      <c r="I9" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -5703,37 +6214,37 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
-      <c r="Y9" s="9" t="s">
+      <c r="Y9" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
-      <c r="AC9" s="9" t="s">
+      <c r="AC9" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
-      <c r="AG9" s="9" t="s">
-        <v>132</v>
+      <c r="AG9" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
-      <c r="AK9" s="10" t="s">
-        <v>133</v>
+      <c r="AK9" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
     </row>
-    <row r="10" spans="1:40" ht="18" customHeight="1">
-      <c r="A10" s="9">
+    <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
         <v>6</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D10" s="3"/>
@@ -5741,8 +6252,8 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="10" t="s">
-        <v>126</v>
+      <c r="I10" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -5759,35 +6270,35 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
-      <c r="Y10" s="9" t="s">
+      <c r="Y10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
-      <c r="AC10" s="9" t="s">
+      <c r="AC10" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
-      <c r="AG10" s="9" t="s">
-        <v>127</v>
+      <c r="AG10" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="AH10" s="3"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
-      <c r="AK10" s="10"/>
+      <c r="AK10" s="6"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
     </row>
-    <row r="11" spans="1:40" ht="18" customHeight="1">
-      <c r="A11" s="9">
+    <row r="11" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
         <v>7</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="3"/>
@@ -5795,8 +6306,8 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="10" t="s">
-        <v>134</v>
+      <c r="I11" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -5813,35 +6324,35 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-      <c r="Y11" s="9" t="s">
+      <c r="Y11" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-      <c r="AC11" s="9" t="s">
+      <c r="AC11" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-      <c r="AG11" s="9" t="s">
-        <v>135</v>
+      <c r="AG11" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
-      <c r="AK11" s="10"/>
+      <c r="AK11" s="6"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:40" ht="18" customHeight="1">
-      <c r="A12" s="9">
+    <row r="12" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D12" s="3"/>
@@ -5849,8 +6360,8 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="10" t="s">
-        <v>136</v>
+      <c r="I12" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -5867,35 +6378,35 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
-      <c r="Y12" s="9" t="s">
+      <c r="Y12" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
-      <c r="AC12" s="9" t="s">
+      <c r="AC12" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
-      <c r="AG12" s="9" t="s">
-        <v>127</v>
+      <c r="AG12" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="AH12" s="3"/>
       <c r="AI12" s="3"/>
       <c r="AJ12" s="3"/>
-      <c r="AK12" s="10"/>
+      <c r="AK12" s="6"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
-    <row r="13" spans="1:40" ht="18" customHeight="1">
-      <c r="A13" s="9">
+    <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
         <v>9</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>80</v>
       </c>
       <c r="D13" s="3"/>
@@ -5903,8 +6414,8 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="10" t="s">
-        <v>137</v>
+      <c r="I13" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -5921,37 +6432,37 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
-      <c r="Y13" s="9" t="s">
+      <c r="Y13" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
-      <c r="AC13" s="9" t="s">
+      <c r="AC13" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
-      <c r="AG13" s="9" t="s">
-        <v>138</v>
+      <c r="AG13" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="AH13" s="3"/>
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
-      <c r="AK13" s="10" t="s">
-        <v>133</v>
+      <c r="AK13" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
     </row>
-    <row r="14" spans="1:40" ht="18" customHeight="1">
-      <c r="A14" s="9">
+    <row r="14" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D14" s="3"/>
@@ -5959,8 +6470,8 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="10" t="s">
-        <v>139</v>
+      <c r="I14" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -5977,35 +6488,35 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
-      <c r="Y14" s="9" t="s">
+      <c r="Y14" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
-      <c r="AC14" s="9" t="s">
+      <c r="AC14" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
-      <c r="AG14" s="9" t="s">
-        <v>140</v>
+      <c r="AG14" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="AH14" s="3"/>
       <c r="AI14" s="3"/>
       <c r="AJ14" s="3"/>
-      <c r="AK14" s="10"/>
+      <c r="AK14" s="6"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
     </row>
-    <row r="15" spans="1:40" ht="18" customHeight="1">
-      <c r="A15" s="9">
+    <row r="15" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
         <v>11</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="6" t="s">
         <v>90</v>
       </c>
       <c r="D15" s="3"/>
@@ -6013,8 +6524,8 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="10" t="s">
-        <v>141</v>
+      <c r="I15" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -6031,46 +6542,46 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
-      <c r="Y15" s="9" t="s">
+      <c r="Y15" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
-      <c r="AC15" s="9" t="s">
+      <c r="AC15" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
-      <c r="AG15" s="9" t="s">
-        <v>142</v>
+      <c r="AG15" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="AH15" s="3"/>
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
-      <c r="AK15" s="10" t="s">
-        <v>133</v>
+      <c r="AK15" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
     </row>
-    <row r="16" spans="1:40" ht="18" customHeight="1">
-      <c r="A16" s="9">
+    <row r="16" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
         <v>12</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="10" t="s">
-        <v>143</v>
+      <c r="C16" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="10" t="s">
-        <v>144</v>
+      <c r="I16" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -6087,43 +6598,113 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="9" t="s">
+      <c r="Y16" s="2" t="s">
         <v>63</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-      <c r="AC16" s="9" t="s">
+      <c r="AC16" s="2" t="s">
         <v>63</v>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-      <c r="AG16" s="9" t="s">
-        <v>145</v>
+      <c r="AG16" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
-      <c r="AK16" s="10" t="s">
-        <v>133</v>
+      <c r="AK16" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
     </row>
-    <row r="18" spans="1:1" ht="14.25">
+    <row r="18" spans="1:1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="AG15:AJ15"/>
-    <mergeCell ref="C4:H4"/>
-    <mergeCell ref="C8:H8"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="AK12:AN12"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="AK9:AN9"/>
+    <mergeCell ref="AG6:AJ6"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="AG9:AJ9"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="Y5:AB5"/>
+    <mergeCell ref="I4:X4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="AG8:AJ8"/>
+    <mergeCell ref="AC7:AF7"/>
+    <mergeCell ref="AC16:AF16"/>
+    <mergeCell ref="AG10:AJ10"/>
+    <mergeCell ref="I16:X16"/>
+    <mergeCell ref="AG11:AJ11"/>
+    <mergeCell ref="Y14:AB14"/>
+    <mergeCell ref="AC12:AF12"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="Y11:AB11"/>
+    <mergeCell ref="Y16:AB16"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="I15:X15"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="AK14:AN14"/>
+    <mergeCell ref="AC14:AF14"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="I12:X12"/>
+    <mergeCell ref="AG13:AJ13"/>
+    <mergeCell ref="Y13:AB13"/>
+    <mergeCell ref="I5:X5"/>
+    <mergeCell ref="I14:X14"/>
+    <mergeCell ref="AK6:AN6"/>
+    <mergeCell ref="AC11:AF11"/>
+    <mergeCell ref="I10:X10"/>
+    <mergeCell ref="AG5:AJ5"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="AK5:AN5"/>
+    <mergeCell ref="AK11:AN11"/>
+    <mergeCell ref="Y6:AB6"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="I9:X9"/>
+    <mergeCell ref="I11:X11"/>
+    <mergeCell ref="AK4:AN4"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="AG7:AJ7"/>
+    <mergeCell ref="Y7:AB7"/>
+    <mergeCell ref="AK10:AN10"/>
+    <mergeCell ref="Y8:AB8"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="Y9:AB9"/>
+    <mergeCell ref="AC4:AF4"/>
+    <mergeCell ref="AC10:AF10"/>
+    <mergeCell ref="AK8:AN8"/>
+    <mergeCell ref="AK7:AN7"/>
+    <mergeCell ref="AC6:AF6"/>
+    <mergeCell ref="AK16:AN16"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="AC9:AF9"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="AG12:AJ12"/>
+    <mergeCell ref="AK13:AN13"/>
+    <mergeCell ref="AC13:AF13"/>
+    <mergeCell ref="AK15:AN15"/>
+    <mergeCell ref="AC15:AF15"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="AG16:AJ16"/>
+    <mergeCell ref="AG14:AJ14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="Y15:AB15"/>
     <mergeCell ref="AE1:AN1"/>
     <mergeCell ref="M1:Z1"/>
     <mergeCell ref="C11:H11"/>
@@ -6140,85 +6721,15 @@
     <mergeCell ref="AA2:AD2"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="C9:H9"/>
+    <mergeCell ref="AG15:AJ15"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="Y12:AB12"/>
-    <mergeCell ref="AK16:AN16"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="AC9:AF9"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="AG12:AJ12"/>
-    <mergeCell ref="AK13:AN13"/>
-    <mergeCell ref="AC13:AF13"/>
-    <mergeCell ref="AK15:AN15"/>
-    <mergeCell ref="AC15:AF15"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="AG16:AJ16"/>
-    <mergeCell ref="AG14:AJ14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="Y15:AB15"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="I9:X9"/>
-    <mergeCell ref="I11:X11"/>
-    <mergeCell ref="AK4:AN4"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="AG7:AJ7"/>
-    <mergeCell ref="Y7:AB7"/>
-    <mergeCell ref="AK10:AN10"/>
-    <mergeCell ref="Y8:AB8"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="Y9:AB9"/>
-    <mergeCell ref="AC4:AF4"/>
-    <mergeCell ref="AC10:AF10"/>
-    <mergeCell ref="AK8:AN8"/>
-    <mergeCell ref="AK7:AN7"/>
-    <mergeCell ref="AC6:AF6"/>
     <mergeCell ref="AC5:AF5"/>
-    <mergeCell ref="AK14:AN14"/>
-    <mergeCell ref="AC14:AF14"/>
-    <mergeCell ref="C5:H5"/>
-    <mergeCell ref="I12:X12"/>
-    <mergeCell ref="AG13:AJ13"/>
-    <mergeCell ref="Y13:AB13"/>
-    <mergeCell ref="I5:X5"/>
-    <mergeCell ref="I14:X14"/>
-    <mergeCell ref="AK6:AN6"/>
-    <mergeCell ref="AC11:AF11"/>
-    <mergeCell ref="I10:X10"/>
-    <mergeCell ref="AG5:AJ5"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="AG8:AJ8"/>
-    <mergeCell ref="AC7:AF7"/>
-    <mergeCell ref="AC16:AF16"/>
-    <mergeCell ref="AG10:AJ10"/>
-    <mergeCell ref="I16:X16"/>
-    <mergeCell ref="AG11:AJ11"/>
-    <mergeCell ref="Y14:AB14"/>
-    <mergeCell ref="AC12:AF12"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="Y11:AB11"/>
-    <mergeCell ref="Y16:AB16"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="I15:X15"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="AK5:AN5"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="AK11:AN11"/>
-    <mergeCell ref="Y6:AB6"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="C7:H7"/>
-    <mergeCell ref="AG9:AJ9"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="Y5:AB5"/>
-    <mergeCell ref="I4:X4"/>
     <mergeCell ref="C12:H12"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="AK12:AN12"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="AK9:AN9"/>
-    <mergeCell ref="AG6:AJ6"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -6232,14 +6743,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN14"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>147</v>
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
+        <v>146</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -6248,13 +6759,13 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="13" t="s">
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -6270,13 +6781,13 @@
       <c r="X1" s="3"/>
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="11" t="s">
+      <c r="AA1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-      <c r="AD1" s="6"/>
-      <c r="AE1" s="9" t="s">
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -6289,7 +6800,7 @@
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
     </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1">
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6298,13 +6809,13 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="13" t="s">
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="7" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -6320,13 +6831,13 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="11" t="s">
+      <c r="AA2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="9"/>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="2"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -6337,71 +6848,71 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
-    <row r="4" spans="1:40">
-      <c r="A4" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="11" t="s">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="11" t="s">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="6"/>
-      <c r="AD4" s="6"/>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="AH4" s="6"/>
-      <c r="AI4" s="6"/>
-      <c r="AJ4" s="6"/>
-      <c r="AK4" s="6"/>
-      <c r="AL4" s="6"/>
-      <c r="AM4" s="6"/>
-      <c r="AN4" s="6"/>
-    </row>
-    <row r="5" spans="1:40" ht="18" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>127</v>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+    </row>
+    <row r="5" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="9" t="s">
-        <v>151</v>
+      <c r="F5" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="10" t="s">
-        <v>152</v>
+      <c r="I5" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -6426,8 +6937,8 @@
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
-      <c r="AG5" s="10" t="s">
-        <v>153</v>
+      <c r="AG5" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
@@ -6437,21 +6948,21 @@
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
-    <row r="6" spans="1:40" ht="18" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>132</v>
+    <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="9" t="s">
-        <v>151</v>
+      <c r="F6" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="10" t="s">
-        <v>154</v>
+      <c r="I6" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -6476,7 +6987,7 @@
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
-      <c r="AG6" s="10"/>
+      <c r="AG6" s="6"/>
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
@@ -6485,21 +6996,21 @@
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
     </row>
-    <row r="7" spans="1:40" ht="18" customHeight="1">
-      <c r="A7" s="9" t="s">
-        <v>135</v>
+    <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-      <c r="F7" s="9" t="s">
-        <v>151</v>
+      <c r="F7" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="10" t="s">
-        <v>155</v>
+      <c r="I7" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -6524,7 +7035,7 @@
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
-      <c r="AG7" s="10"/>
+      <c r="AG7" s="6"/>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
@@ -6533,21 +7044,21 @@
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
     </row>
-    <row r="8" spans="1:40" ht="18" customHeight="1">
-      <c r="A8" s="9" t="s">
-        <v>138</v>
+    <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-      <c r="F8" s="9" t="s">
-        <v>151</v>
+      <c r="F8" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="10" t="s">
-        <v>156</v>
+      <c r="I8" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -6572,7 +7083,7 @@
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
-      <c r="AG8" s="10"/>
+      <c r="AG8" s="6"/>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
@@ -6581,21 +7092,21 @@
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
-    <row r="9" spans="1:40" ht="18" customHeight="1">
-      <c r="A9" s="9" t="s">
-        <v>129</v>
+    <row r="9" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-      <c r="F9" s="9" t="s">
-        <v>151</v>
+      <c r="F9" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="10" t="s">
-        <v>157</v>
+      <c r="I9" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -6620,8 +7131,8 @@
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
-      <c r="AG9" s="10" t="s">
-        <v>153</v>
+      <c r="AG9" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
@@ -6631,21 +7142,21 @@
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
     </row>
-    <row r="10" spans="1:40" ht="18" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>142</v>
+    <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-      <c r="F10" s="9" t="s">
-        <v>151</v>
+      <c r="F10" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="10" t="s">
-        <v>158</v>
+      <c r="I10" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -6670,7 +7181,7 @@
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
-      <c r="AG10" s="10"/>
+      <c r="AG10" s="6"/>
       <c r="AH10" s="3"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
@@ -6679,21 +7190,21 @@
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
     </row>
-    <row r="11" spans="1:40" ht="27.95" customHeight="1">
-      <c r="A11" s="9" t="s">
-        <v>140</v>
+    <row r="11" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="9" t="s">
-        <v>151</v>
+      <c r="F11" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="10" t="s">
-        <v>159</v>
+      <c r="I11" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -6718,8 +7229,8 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-      <c r="AG11" s="10" t="s">
-        <v>160</v>
+      <c r="AG11" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
@@ -6729,21 +7240,21 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:40" ht="18" customHeight="1">
-      <c r="A12" s="9" t="s">
-        <v>145</v>
+    <row r="12" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="2" t="s">
+        <v>144</v>
       </c>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="9" t="s">
-        <v>151</v>
+      <c r="F12" s="2" t="s">
+        <v>150</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="10" t="s">
-        <v>161</v>
+      <c r="I12" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -6768,8 +7279,8 @@
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
-      <c r="AG12" s="10" t="s">
-        <v>162</v>
+      <c r="AG12" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="AH12" s="3"/>
       <c r="AI12" s="3"/>
@@ -6779,21 +7290,21 @@
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
-    <row r="13" spans="1:40" ht="18" customHeight="1">
-      <c r="A13" s="9" t="s">
-        <v>179</v>
+    <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="9" t="s">
-        <v>180</v>
+      <c r="F13" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="10" t="s">
-        <v>181</v>
+      <c r="I13" s="6" t="s">
+        <v>180</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -6818,7 +7329,7 @@
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
-      <c r="AG13" s="10"/>
+      <c r="AG13" s="6"/>
       <c r="AH13" s="3"/>
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
@@ -6827,21 +7338,21 @@
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
     </row>
-    <row r="14" spans="1:40" ht="18" customHeight="1">
-      <c r="A14" s="9" t="s">
-        <v>182</v>
+    <row r="14" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="9" t="s">
-        <v>183</v>
+      <c r="F14" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="10" t="s">
-        <v>184</v>
+      <c r="I14" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -6866,7 +7377,7 @@
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
-      <c r="AG14" s="10"/>
+      <c r="AG14" s="6"/>
       <c r="AH14" s="3"/>
       <c r="AI14" s="3"/>
       <c r="AJ14" s="3"/>
@@ -6877,6 +7388,43 @@
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:AF13"/>
+    <mergeCell ref="AG13:AN13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:AF14"/>
+    <mergeCell ref="AG14:AN14"/>
+    <mergeCell ref="AG12:AN12"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="I6:AF6"/>
+    <mergeCell ref="I11:AF11"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="AG8:AN8"/>
+    <mergeCell ref="I12:AF12"/>
+    <mergeCell ref="AG6:AN6"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="I7:AF7"/>
+    <mergeCell ref="AG10:AN10"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="AG11:AN11"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I5:AF5"/>
+    <mergeCell ref="I8:AF8"/>
+    <mergeCell ref="I4:AF4"/>
+    <mergeCell ref="AG7:AN7"/>
+    <mergeCell ref="I10:AF10"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="AA2:AD2"/>
+    <mergeCell ref="A6:E6"/>
     <mergeCell ref="M1:Z1"/>
     <mergeCell ref="AG9:AN9"/>
     <mergeCell ref="AA1:AD1"/>
@@ -6893,43 +7441,6 @@
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="AG4:AN4"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="AG11:AN11"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I5:AF5"/>
-    <mergeCell ref="I8:AF8"/>
-    <mergeCell ref="I4:AF4"/>
-    <mergeCell ref="AG7:AN7"/>
-    <mergeCell ref="I10:AF10"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="AA2:AD2"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="AG12:AN12"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="I6:AF6"/>
-    <mergeCell ref="I11:AF11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="AG8:AN8"/>
-    <mergeCell ref="I12:AF12"/>
-    <mergeCell ref="AG6:AN6"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="I7:AF7"/>
-    <mergeCell ref="AG10:AN10"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:AF13"/>
-    <mergeCell ref="AG13:AN13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:AF14"/>
-    <mergeCell ref="AG14:AN14"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/doc/excel/화면설계서_X1_항공편검색.xlsx
+++ b/doc/excel/화면설계서_X1_항공편검색.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\gwx\java\SpringLab01\doc\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49ED7617-D794-417E-B1EF-7FA7FF1E2FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0FA9B1-AAE5-4ADB-8246-C1368D28E6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1890" yWindow="1950" windowWidth="20295" windowHeight="12060" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,16 @@
     <sheet name="화면항목정의" sheetId="5" r:id="rId5"/>
     <sheet name="이벤트정의" sheetId="6" r:id="rId6"/>
     <sheet name="사용API" sheetId="9" r:id="rId7"/>
-    <sheet name="입력체크" sheetId="7" r:id="rId8"/>
-    <sheet name="메시지목록" sheetId="8" r:id="rId9"/>
+    <sheet name="사용컴포넌트" sheetId="10" r:id="rId8"/>
+    <sheet name="입력체크" sheetId="7" r:id="rId9"/>
+    <sheet name="메시지목록" sheetId="8" r:id="rId10"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="247">
   <si>
     <t>HOSHIMOTO AIR 항공권 예약 시스템</t>
   </si>
@@ -370,9 +371,6 @@
   </si>
   <si>
     <t>검색</t>
-  </si>
-  <si>
-    <t>항목 No.11 클릭</t>
   </si>
   <si>
     <t>X2</t>
@@ -539,14 +537,6 @@
   <si>
     <t>・선택한 공항을 도착지로 설정한다.
 ・출발지 드롭다운 목록에서 선택한 공항을 제외한다.(E002 예방)</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>・왕복 탭을 선택 상태로 한다.
-・성인 인원에 1, 유아 인원에 0을 설정한다.
-・공항 목록(X0: GET /api/airports)을 조회하여 출발지·도착지 드롭다운에 표시한다.
-　조회 실패 시 E009를 표시한다.
-・그 밖의 입력 항목은 공란으로 한다.</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -554,14 +544,6 @@
 ・유아 인원이 0일 때 「−」를 비활성화한다.
 ・유아 인원이 성인 인원과 같을 때 「＋」를 비활성화한다.
 ・성인 인원과 유아 인원의 합계가 9일 때 「＋」를 비활성화한다.</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1. 입력 체크(클라이언트)를 수행한다. 에러 시 메시지를 표시하고 처리를 중단한다.. 검색 조건을 쿼리 파라미터로 하여 GET /api/flights 를 전송한다.
-　※ 1단계는 출발지·도착지만 전송한다.(specs X1 참조). 입력 체크(서버)를 수행한다.
-　・에러 있음: 화면을 이동하지 않고, 입력값을 유지한 채 에러 메시지를 표시한다.
-　・에러 없음: X2 항공편 목록을 표시한다.
-　・결과 0건: X2에 I001을 표시한다.</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -1210,12 +1192,308 @@
     </r>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">왕복 탭을 선택 상태로 한다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">성인 인원에 1, 유아 인원에 0을 설정한다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">공항 목록(X0: GET /api/airports)을 조회하여 출발지·도착지 드롭다운에 표시한다.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>　조회 실패 시 E009를 표시한다.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그 밖의 입력 항목은 공란으로 한다.</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>항목 No.11 클릭</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <r>
+      <t>1. 입력 체크(클라이언트)를 수행한다. 에러 시 메시지를 표시하고 처리를 중단한다.
+2. 검색 조건을 쿼리 파라미터로 하여 GET /api/flights 를 전송한다.
+　※ 1단계는 출발지·도착지만 전송한다.(specs X1 참조)
+3. 입력 체크(서버)를 수행한다.
+　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에러 있음: 화면을 이동하지 않고, 입력값을 유지한 채 에러 메시지를 표시한다.
+　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에러 없음: X2 항공편 목록을 표시한다.
+　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결과 0건: X2에 I001을 표시한다.</t>
+    </r>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>frontend/src/features/home/components/X1_FlightSearchBar.tsx
+（공통 부품: C1_AirportSelect.tsx, 「사용컴포넌트」 시트 참조）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>사용컴포넌트</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>사용 화면</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>비고</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>파일</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>props</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>컴포넌트명</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>역할</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>부품ID</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>대응 항목</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X1</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>이벤트정의 No.2~8</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>features/home/components/X1_FlightSearchBar.tsx</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>화면 전용</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>없음</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X1_FlightSearchBar</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>검색바 전체(왕복/편도, 출발지·도착지, 인원, 검색 버튼)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>화면항목정의 No.3~11</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>이벤트정의 No.4, 5</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>features/home/components/C1_AirportSelect.tsx</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>공통</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>・label
+・airports
+・value
+・onSelect</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>C1_AirportSelect</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>공항 드롭다운. 「공항명 (공항코드)」 형식으로 표시</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>C1</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>화면항목정의 No.5, 6</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>※ 부품ID 규칙: 화면 전용은 {화면ID}_{PascalCase}, 공통은 C{번호}_{PascalCase}（frontend/CLAUDE.md）. 공통 부품을 다른 화면에서도 쓰게 되면 「사용 화면」에 추가한다.</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>화면개요, 사용컴포넌트</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>템플릿에 X1_FlightSearchBar.tsx 기입, 사용컴포넌트 시트 신규 추가(X1_FlightSearchBar, C1_AirportSelect)</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1301,6 +1579,19 @@
     <font>
       <sz val="9"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -1403,18 +1694,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1473,16 +1774,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1834,7 +2125,7 @@
   </cols>
   <sheetData>
     <row r="8" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="15" t="s">
         <v>0</v>
       </c>
       <c r="F8" s="3"/>
@@ -1938,145 +2229,145 @@
       <c r="AJ10" s="3"/>
     </row>
     <row r="12" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="13"/>
-      <c r="AC12" s="13"/>
-      <c r="AD12" s="13"/>
-      <c r="AE12" s="13"/>
-      <c r="AF12" s="13"/>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="13"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="17"/>
+      <c r="M12" s="17"/>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="17"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="17"/>
+      <c r="W12" s="17"/>
+      <c r="X12" s="17"/>
+      <c r="Y12" s="17"/>
+      <c r="Z12" s="17"/>
+      <c r="AA12" s="17"/>
+      <c r="AB12" s="17"/>
+      <c r="AC12" s="17"/>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+      <c r="AF12" s="17"/>
+      <c r="AG12" s="17"/>
+      <c r="AH12" s="17"/>
+      <c r="AI12" s="17"/>
+      <c r="AJ12" s="17"/>
     </row>
     <row r="13" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="13"/>
-      <c r="V13" s="13"/>
-      <c r="W13" s="13"/>
-      <c r="X13" s="13"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="13"/>
-      <c r="AA13" s="13"/>
-      <c r="AB13" s="13"/>
-      <c r="AC13" s="13"/>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="13"/>
-      <c r="AF13" s="13"/>
-      <c r="AG13" s="13"/>
-      <c r="AH13" s="13"/>
-      <c r="AI13" s="13"/>
-      <c r="AJ13" s="13"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="17"/>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17"/>
+      <c r="Q13" s="17"/>
+      <c r="R13" s="17"/>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="17"/>
+      <c r="W13" s="17"/>
+      <c r="X13" s="17"/>
+      <c r="Y13" s="17"/>
+      <c r="Z13" s="17"/>
+      <c r="AA13" s="17"/>
+      <c r="AB13" s="17"/>
+      <c r="AC13" s="17"/>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+      <c r="AF13" s="17"/>
+      <c r="AG13" s="17"/>
+      <c r="AH13" s="17"/>
+      <c r="AI13" s="17"/>
+      <c r="AJ13" s="17"/>
     </row>
     <row r="14" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="13"/>
-      <c r="V14" s="13"/>
-      <c r="W14" s="13"/>
-      <c r="X14" s="13"/>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="13"/>
-      <c r="AA14" s="13"/>
-      <c r="AB14" s="13"/>
-      <c r="AC14" s="13"/>
-      <c r="AD14" s="13"/>
-      <c r="AE14" s="13"/>
-      <c r="AF14" s="13"/>
-      <c r="AG14" s="13"/>
-      <c r="AH14" s="13"/>
-      <c r="AI14" s="13"/>
-      <c r="AJ14" s="13"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="17"/>
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="17"/>
+      <c r="T14" s="17"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="17"/>
+      <c r="W14" s="17"/>
+      <c r="X14" s="17"/>
+      <c r="Y14" s="17"/>
+      <c r="Z14" s="17"/>
+      <c r="AA14" s="17"/>
+      <c r="AB14" s="17"/>
+      <c r="AC14" s="17"/>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="17"/>
+      <c r="AF14" s="17"/>
+      <c r="AG14" s="17"/>
+      <c r="AH14" s="17"/>
+      <c r="AI14" s="17"/>
+      <c r="AJ14" s="17"/>
     </row>
     <row r="15" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
-      <c r="AE15" s="13"/>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="13"/>
-      <c r="AH15" s="13"/>
-      <c r="AI15" s="13"/>
-      <c r="AJ15" s="13"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="17"/>
+      <c r="O15" s="17"/>
+      <c r="P15" s="17"/>
+      <c r="Q15" s="17"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="17"/>
+      <c r="T15" s="17"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="17"/>
+      <c r="W15" s="17"/>
+      <c r="X15" s="17"/>
+      <c r="Y15" s="17"/>
+      <c r="Z15" s="17"/>
+      <c r="AA15" s="17"/>
+      <c r="AB15" s="17"/>
+      <c r="AC15" s="17"/>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+      <c r="AF15" s="17"/>
+      <c r="AG15" s="17"/>
+      <c r="AH15" s="17"/>
+      <c r="AI15" s="17"/>
+      <c r="AJ15" s="17"/>
     </row>
     <row r="17" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="15" t="s">
         <v>2</v>
       </c>
       <c r="F17" s="3"/>
@@ -2146,7 +2437,7 @@
       <c r="AJ18" s="3"/>
     </row>
     <row r="22" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="M22" s="9" t="s">
+      <c r="M22" s="13" t="s">
         <v>3</v>
       </c>
       <c r="N22" s="5"/>
@@ -2154,7 +2445,7 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
-      <c r="S22" s="10" t="s">
+      <c r="S22" s="14" t="s">
         <v>4</v>
       </c>
       <c r="T22" s="3"/>
@@ -2186,7 +2477,7 @@
       <c r="AB23" s="3"/>
     </row>
     <row r="24" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="M24" s="9" t="s">
+      <c r="M24" s="13" t="s">
         <v>5</v>
       </c>
       <c r="N24" s="5"/>
@@ -2194,7 +2485,7 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
-      <c r="S24" s="10" t="s">
+      <c r="S24" s="14" t="s">
         <v>6</v>
       </c>
       <c r="T24" s="3"/>
@@ -2226,7 +2517,7 @@
       <c r="AB25" s="3"/>
     </row>
     <row r="26" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="M26" s="9" t="s">
+      <c r="M26" s="13" t="s">
         <v>7</v>
       </c>
       <c r="N26" s="5"/>
@@ -2234,7 +2525,7 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
-      <c r="S26" s="10"/>
+      <c r="S26" s="14"/>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
@@ -2264,7 +2555,7 @@
       <c r="AB27" s="3"/>
     </row>
     <row r="28" spans="5:36" x14ac:dyDescent="0.15">
-      <c r="M28" s="9" t="s">
+      <c r="M28" s="13" t="s">
         <v>8</v>
       </c>
       <c r="N28" s="5"/>
@@ -2272,7 +2563,7 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
-      <c r="S28" s="10"/>
+      <c r="S28" s="14"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
@@ -2321,8 +2612,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2333,8 +2624,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>9</v>
+      <c r="A1" s="12" t="s">
+        <v>145</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -2349,7 +2640,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -2371,7 +2662,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -2399,7 +2690,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -2421,7 +2712,718 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" s="2"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
+      <c r="P4" s="5"/>
+      <c r="Q4" s="5"/>
+      <c r="R4" s="5"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="5"/>
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+      <c r="AA4" s="5"/>
+      <c r="AB4" s="5"/>
+      <c r="AC4" s="5"/>
+      <c r="AD4" s="5"/>
+      <c r="AE4" s="5"/>
+      <c r="AF4" s="5"/>
+      <c r="AG4" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH4" s="5"/>
+      <c r="AI4" s="5"/>
+      <c r="AJ4" s="5"/>
+      <c r="AK4" s="5"/>
+      <c r="AL4" s="5"/>
+      <c r="AM4" s="5"/>
+      <c r="AN4" s="5"/>
+    </row>
+    <row r="5" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J5" s="3"/>
+      <c r="K5" s="3"/>
+      <c r="L5" s="3"/>
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="U5" s="3"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="3"/>
+      <c r="X5" s="3"/>
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
+      <c r="AB5" s="3"/>
+      <c r="AC5" s="3"/>
+      <c r="AD5" s="3"/>
+      <c r="AE5" s="3"/>
+      <c r="AF5" s="3"/>
+      <c r="AG5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH5" s="3"/>
+      <c r="AI5" s="3"/>
+      <c r="AJ5" s="3"/>
+      <c r="AK5" s="3"/>
+      <c r="AL5" s="3"/>
+      <c r="AM5" s="3"/>
+      <c r="AN5" s="3"/>
+    </row>
+    <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3"/>
+      <c r="R6" s="3"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+      <c r="U6" s="3"/>
+      <c r="V6" s="3"/>
+      <c r="W6" s="3"/>
+      <c r="X6" s="3"/>
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
+      <c r="AB6" s="3"/>
+      <c r="AC6" s="3"/>
+      <c r="AD6" s="3"/>
+      <c r="AE6" s="3"/>
+      <c r="AF6" s="3"/>
+      <c r="AG6" s="2"/>
+      <c r="AH6" s="3"/>
+      <c r="AI6" s="3"/>
+      <c r="AJ6" s="3"/>
+      <c r="AK6" s="3"/>
+      <c r="AL6" s="3"/>
+      <c r="AM6" s="3"/>
+      <c r="AN6" s="3"/>
+    </row>
+    <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="2"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+    </row>
+    <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="2"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+    </row>
+    <row r="9" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+    </row>
+    <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="2"/>
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+    </row>
+    <row r="11" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+    </row>
+    <row r="12" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+    </row>
+    <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="2"/>
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="3"/>
+      <c r="AN13" s="3"/>
+    </row>
+    <row r="14" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+      <c r="W14" s="3"/>
+      <c r="X14" s="3"/>
+      <c r="Y14" s="3"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
+      <c r="AB14" s="3"/>
+      <c r="AC14" s="3"/>
+      <c r="AD14" s="3"/>
+      <c r="AE14" s="3"/>
+      <c r="AF14" s="3"/>
+      <c r="AG14" s="2"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3"/>
+      <c r="AJ14" s="3"/>
+      <c r="AK14" s="3"/>
+      <c r="AL14" s="3"/>
+      <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="53">
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="I13:AF13"/>
+    <mergeCell ref="AG13:AN13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:AF14"/>
+    <mergeCell ref="AG14:AN14"/>
+    <mergeCell ref="AG12:AN12"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="I6:AF6"/>
+    <mergeCell ref="I11:AF11"/>
+    <mergeCell ref="F12:H12"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="AG8:AN8"/>
+    <mergeCell ref="I12:AF12"/>
+    <mergeCell ref="AG6:AN6"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="I7:AF7"/>
+    <mergeCell ref="AG10:AN10"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="AG11:AN11"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="I5:AF5"/>
+    <mergeCell ref="I8:AF8"/>
+    <mergeCell ref="I4:AF4"/>
+    <mergeCell ref="AG7:AN7"/>
+    <mergeCell ref="I10:AF10"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="AA2:AD2"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="AG9:AN9"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="F11:H11"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="F10:H10"/>
+    <mergeCell ref="I9:AF9"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="AG5:AN5"/>
+    <mergeCell ref="AE1:AN1"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="AG4:AN4"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AN15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="40" width="3.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+    </row>
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="10"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -2485,19 +3487,19 @@
       <c r="AN4" s="5"/>
     </row>
     <row r="5" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="J5" s="3"/>
@@ -2507,7 +3509,7 @@
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="2" t="s">
         <v>17</v>
       </c>
       <c r="R5" s="3"/>
@@ -2527,7 +3529,7 @@
       <c r="AF5" s="3"/>
       <c r="AG5" s="3"/>
       <c r="AH5" s="3"/>
-      <c r="AI5" s="2"/>
+      <c r="AI5" s="10"/>
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
@@ -2535,20 +3537,20 @@
       <c r="AN5" s="3"/>
     </row>
     <row r="6" spans="1:40" ht="48" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
+      <c r="A6" s="10">
         <v>1.1000000000000001</v>
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="14">
+      <c r="D6" s="18">
         <v>46309</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="6" t="s">
-        <v>184</v>
+      <c r="I6" s="2" t="s">
+        <v>181</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -2557,8 +3559,8 @@
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
-      <c r="Q6" s="6" t="s">
-        <v>185</v>
+      <c r="Q6" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -2577,7 +3579,7 @@
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
-      <c r="AI6" s="2"/>
+      <c r="AI6" s="10"/>
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
@@ -2585,20 +3587,20 @@
       <c r="AN6" s="3"/>
     </row>
     <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="2">
+      <c r="A7" s="10">
         <v>1.2</v>
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
-      <c r="D7" s="14">
+      <c r="D7" s="18">
         <v>46309</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="6" t="s">
-        <v>186</v>
+      <c r="I7" s="2" t="s">
+        <v>183</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -2607,8 +3609,8 @@
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
-      <c r="Q7" s="6" t="s">
-        <v>214</v>
+      <c r="Q7" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -2627,7 +3629,7 @@
       <c r="AF7" s="3"/>
       <c r="AG7" s="3"/>
       <c r="AH7" s="3"/>
-      <c r="AI7" s="2"/>
+      <c r="AI7" s="10"/>
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
@@ -2635,15 +3637,21 @@
       <c r="AN7" s="3"/>
     </row>
     <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2"/>
+      <c r="A8" s="10">
+        <v>1.3</v>
+      </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
+      <c r="D8" s="18">
+        <v>46311</v>
+      </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="6"/>
+      <c r="I8" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -2651,7 +3659,9 @@
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
-      <c r="Q8" s="6"/>
+      <c r="Q8" s="2" t="s">
+        <v>246</v>
+      </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
@@ -2669,7 +3679,7 @@
       <c r="AF8" s="3"/>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
-      <c r="AI8" s="2"/>
+      <c r="AI8" s="10"/>
       <c r="AJ8" s="3"/>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3"/>
@@ -2677,15 +3687,15 @@
       <c r="AN8" s="3"/>
     </row>
     <row r="9" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2"/>
+      <c r="A9" s="10"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="6"/>
+      <c r="I9" s="2"/>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -2693,7 +3703,7 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="6"/>
+      <c r="Q9" s="2"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -2711,7 +3721,7 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
-      <c r="AI9" s="2"/>
+      <c r="AI9" s="10"/>
       <c r="AJ9" s="3"/>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
@@ -2719,15 +3729,15 @@
       <c r="AN9" s="3"/>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="6"/>
+      <c r="I10" s="2"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -2735,7 +3745,7 @@
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="Q10" s="6"/>
+      <c r="Q10" s="2"/>
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
@@ -2753,7 +3763,7 @@
       <c r="AF10" s="3"/>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
-      <c r="AI10" s="2"/>
+      <c r="AI10" s="10"/>
       <c r="AJ10" s="3"/>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3"/>
@@ -2761,15 +3771,15 @@
       <c r="AN10" s="3"/>
     </row>
     <row r="11" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="6"/>
+      <c r="I11" s="2"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -2777,7 +3787,7 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-      <c r="Q11" s="6"/>
+      <c r="Q11" s="2"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
@@ -2795,7 +3805,7 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-      <c r="AI11" s="2"/>
+      <c r="AI11" s="10"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
@@ -2803,15 +3813,15 @@
       <c r="AN11" s="3"/>
     </row>
     <row r="12" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="6"/>
+      <c r="I12" s="2"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -2819,7 +3829,7 @@
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
-      <c r="Q12" s="6"/>
+      <c r="Q12" s="2"/>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
@@ -2837,7 +3847,7 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
-      <c r="AI12" s="2"/>
+      <c r="AI12" s="10"/>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
@@ -2845,15 +3855,15 @@
       <c r="AN12" s="3"/>
     </row>
     <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2"/>
+      <c r="A13" s="10"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
-      <c r="D13" s="2"/>
+      <c r="D13" s="10"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="6"/>
+      <c r="I13" s="2"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -2861,7 +3871,7 @@
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
-      <c r="Q13" s="6"/>
+      <c r="Q13" s="2"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
@@ -2879,7 +3889,7 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
-      <c r="AI13" s="2"/>
+      <c r="AI13" s="10"/>
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
@@ -2887,15 +3897,15 @@
       <c r="AN13" s="3"/>
     </row>
     <row r="14" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2"/>
+      <c r="A14" s="10"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="6"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -2903,7 +3913,7 @@
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
-      <c r="Q14" s="6"/>
+      <c r="Q14" s="2"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
@@ -2921,48 +3931,91 @@
       <c r="AF14" s="3"/>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
-      <c r="AI14" s="2"/>
+      <c r="AI14" s="10"/>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
     </row>
+    <row r="15" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="10"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="10"/>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="64">
-    <mergeCell ref="D13:H13"/>
+  <mergeCells count="69">
+    <mergeCell ref="AI8:AN8"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="Q15:AH15"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="I13:P13"/>
     <mergeCell ref="A14:C14"/>
-    <mergeCell ref="Q14:AH14"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="I12:P12"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="Q11:AH11"/>
-    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="Q12:AH12"/>
+    <mergeCell ref="A10:C10"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="I5:P5"/>
-    <mergeCell ref="Q9:AH9"/>
+    <mergeCell ref="Q10:AH10"/>
     <mergeCell ref="I2:L2"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="A1:H2"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="I13:P13"/>
-    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="I14:P14"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="Q4:AH4"/>
     <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D12:H12"/>
     <mergeCell ref="AA1:AD1"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="Q8:AH8"/>
+    <mergeCell ref="Q9:AH9"/>
     <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
     <mergeCell ref="Q7:AH7"/>
-    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="D9:H9"/>
     <mergeCell ref="I4:P4"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="Q12:AH12"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="Q13:AH13"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="A5:C5"/>
@@ -2971,29 +4024,33 @@
     <mergeCell ref="I7:P7"/>
     <mergeCell ref="AA2:AD2"/>
     <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="I8:P8"/>
+    <mergeCell ref="Q8:AH8"/>
+    <mergeCell ref="AI12:AN12"/>
+    <mergeCell ref="Q11:AH11"/>
+    <mergeCell ref="I12:P12"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="I11:P11"/>
+    <mergeCell ref="AI15:AN15"/>
+    <mergeCell ref="AI14:AN14"/>
+    <mergeCell ref="I9:P9"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="Q14:AH14"/>
     <mergeCell ref="AI11:AN11"/>
-    <mergeCell ref="Q10:AH10"/>
-    <mergeCell ref="I11:P11"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="I9:P9"/>
-    <mergeCell ref="I10:P10"/>
-    <mergeCell ref="AI14:AN14"/>
-    <mergeCell ref="AI13:AN13"/>
-    <mergeCell ref="I8:P8"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="Q13:AH13"/>
-    <mergeCell ref="AI10:AN10"/>
     <mergeCell ref="AI6:AN6"/>
     <mergeCell ref="I6:P6"/>
     <mergeCell ref="Q5:AH5"/>
+    <mergeCell ref="AI10:AN10"/>
+    <mergeCell ref="AI13:AN13"/>
+    <mergeCell ref="AI5:AN5"/>
     <mergeCell ref="AI9:AN9"/>
-    <mergeCell ref="AI12:AN12"/>
-    <mergeCell ref="AI5:AN5"/>
-    <mergeCell ref="AI8:AN8"/>
     <mergeCell ref="AI7:AN7"/>
     <mergeCell ref="AI4:AN4"/>
-    <mergeCell ref="I14:P14"/>
+    <mergeCell ref="I15:P15"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -3013,7 +4070,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>18</v>
       </c>
       <c r="B1" s="3"/>
@@ -3029,7 +4086,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -3051,7 +4108,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -3079,7 +4136,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -3101,7 +4158,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" s="2"/>
+      <c r="AE2" s="10"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -3123,7 +4180,7 @@
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="3"/>
@@ -3169,7 +4226,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="3"/>
@@ -3215,7 +4272,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="8" t="s">
         <v>24</v>
       </c>
       <c r="J6" s="3"/>
@@ -3261,7 +4318,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>26</v>
       </c>
       <c r="J7" s="3"/>
@@ -3307,8 +4364,8 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
-      <c r="I8" s="7" t="s">
-        <v>177</v>
+      <c r="I8" s="8" t="s">
+        <v>174</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3342,7 +4399,7 @@
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
-    <row r="9" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:40" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
@@ -3353,8 +4410,8 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
-      <c r="I9" s="7" t="s">
-        <v>29</v>
+      <c r="I9" s="8" t="s">
+        <v>216</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -3399,7 +4456,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="8" t="s">
         <v>29</v>
       </c>
       <c r="J10" s="3"/>
@@ -3445,7 +4502,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>32</v>
       </c>
       <c r="J11" s="3"/>
@@ -3491,7 +4548,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="8" t="s">
         <v>34</v>
       </c>
       <c r="J12" s="3"/>
@@ -3537,7 +4594,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="8" t="s">
         <v>36</v>
       </c>
       <c r="J13" s="3"/>
@@ -3583,7 +4640,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="8" t="s">
         <v>38</v>
       </c>
       <c r="J14" s="3"/>
@@ -3670,7 +4727,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>39</v>
       </c>
       <c r="B1" s="3"/>
@@ -3686,7 +4743,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -3708,7 +4765,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -3736,7 +4793,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -3758,7 +4815,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" s="2"/>
+      <c r="AE2" s="10"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -3805,7 +4862,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>41</v>
       </c>
       <c r="B1" s="3"/>
@@ -3821,7 +4878,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -3843,7 +4900,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -3871,7 +4928,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -3893,7 +4950,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" s="2"/>
+      <c r="AE2" s="10"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -3965,18 +5022,18 @@
       <c r="AN4" s="5"/>
     </row>
     <row r="5" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>50</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="I5" s="3"/>
@@ -3985,34 +5042,34 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="10" t="s">
         <v>52</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="S5" s="2" t="s">
+      <c r="S5" s="10" t="s">
         <v>53</v>
       </c>
       <c r="T5" s="3"/>
-      <c r="U5" s="2" t="s">
+      <c r="U5" s="10" t="s">
         <v>51</v>
       </c>
       <c r="V5" s="3"/>
-      <c r="W5" s="6" t="s">
+      <c r="W5" s="2" t="s">
         <v>51</v>
       </c>
       <c r="X5" s="3"/>
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
-      <c r="AB5" s="6" t="s">
+      <c r="AB5" s="2" t="s">
         <v>54</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
-      <c r="AF5" s="6" t="s">
+      <c r="AF5" s="2" t="s">
         <v>55</v>
       </c>
       <c r="AG5" s="3"/>
@@ -4025,18 +5082,18 @@
       <c r="AN5" s="3"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
+      <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>56</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="2" t="s">
         <v>51</v>
       </c>
       <c r="I6" s="3"/>
@@ -4045,34 +5102,34 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="2" t="s">
+      <c r="O6" s="10" t="s">
         <v>57</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-      <c r="S6" s="2" t="s">
+      <c r="S6" s="10" t="s">
         <v>53</v>
       </c>
       <c r="T6" s="3"/>
-      <c r="U6" s="2" t="s">
+      <c r="U6" s="10" t="s">
         <v>51</v>
       </c>
       <c r="V6" s="3"/>
-      <c r="W6" s="6" t="s">
+      <c r="W6" s="2" t="s">
         <v>51</v>
       </c>
       <c r="X6" s="3"/>
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
-      <c r="AB6" s="6" t="s">
+      <c r="AB6" s="2" t="s">
         <v>58</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
-      <c r="AF6" s="6"/>
+      <c r="AF6" s="2"/>
       <c r="AG6" s="3"/>
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
@@ -4083,18 +5140,18 @@
       <c r="AN6" s="3"/>
     </row>
     <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="2">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>59</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I7" s="3"/>
@@ -4103,34 +5160,34 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="2" t="s">
+      <c r="O7" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-      <c r="S7" s="2" t="s">
+      <c r="S7" s="10" t="s">
         <v>62</v>
       </c>
       <c r="T7" s="3"/>
-      <c r="U7" s="2" t="s">
+      <c r="U7" s="10" t="s">
         <v>63</v>
       </c>
       <c r="V7" s="3"/>
-      <c r="W7" s="6" t="s">
+      <c r="W7" s="2" t="s">
         <v>64</v>
       </c>
       <c r="X7" s="3"/>
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
-      <c r="AB7" s="6" t="s">
+      <c r="AB7" s="2" t="s">
         <v>65</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
-      <c r="AF7" s="6" t="s">
+      <c r="AF7" s="2" t="s">
         <v>66</v>
       </c>
       <c r="AG7" s="3"/>
@@ -4143,18 +5200,18 @@
       <c r="AN7" s="3"/>
     </row>
     <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="2" t="s">
         <v>60</v>
       </c>
       <c r="I8" s="3"/>
@@ -4163,34 +5220,34 @@
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
-      <c r="O8" s="2" t="s">
+      <c r="O8" s="10" t="s">
         <v>61</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="S8" s="2" t="s">
+      <c r="S8" s="10" t="s">
         <v>62</v>
       </c>
       <c r="T8" s="3"/>
-      <c r="U8" s="2" t="s">
+      <c r="U8" s="10" t="s">
         <v>63</v>
       </c>
       <c r="V8" s="3"/>
-      <c r="W8" s="6" t="s">
+      <c r="W8" s="2" t="s">
         <v>68</v>
       </c>
       <c r="X8" s="3"/>
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
-      <c r="AB8" s="6" t="s">
+      <c r="AB8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
-      <c r="AF8" s="6" t="s">
+      <c r="AF8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="AG8" s="3"/>
@@ -4203,18 +5260,18 @@
       <c r="AN8" s="3"/>
     </row>
     <row r="9" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2">
+      <c r="A9" s="10">
         <v>5</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="2" t="s">
         <v>72</v>
       </c>
       <c r="I9" s="3"/>
@@ -4223,35 +5280,35 @@
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="2" t="s">
-        <v>171</v>
+      <c r="O9" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="S9" s="2" t="s">
+      <c r="S9" s="10" t="s">
         <v>62</v>
       </c>
       <c r="T9" s="3"/>
-      <c r="U9" s="2" t="s">
+      <c r="U9" s="10" t="s">
         <v>63</v>
       </c>
       <c r="V9" s="3"/>
-      <c r="W9" s="6" t="s">
-        <v>172</v>
+      <c r="W9" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="X9" s="3"/>
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
-      <c r="AB9" s="6" t="s">
-        <v>173</v>
+      <c r="AB9" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
-      <c r="AF9" s="6" t="s">
-        <v>174</v>
+      <c r="AF9" s="2" t="s">
+        <v>171</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -4263,18 +5320,18 @@
       <c r="AN9" s="3"/>
     </row>
     <row r="10" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2">
+      <c r="A10" s="10">
         <v>6</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="2" t="s">
         <v>75</v>
       </c>
       <c r="I10" s="3"/>
@@ -4283,35 +5340,35 @@
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="2" t="s">
-        <v>171</v>
+      <c r="O10" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="2" t="s">
+      <c r="S10" s="10" t="s">
         <v>62</v>
       </c>
       <c r="T10" s="3"/>
-      <c r="U10" s="2" t="s">
+      <c r="U10" s="10" t="s">
         <v>63</v>
       </c>
       <c r="V10" s="3"/>
-      <c r="W10" s="6" t="s">
-        <v>172</v>
+      <c r="W10" s="2" t="s">
+        <v>169</v>
       </c>
       <c r="X10" s="3"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
-      <c r="AB10" s="6" t="s">
-        <v>173</v>
+      <c r="AB10" s="2" t="s">
+        <v>170</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
-      <c r="AF10" s="6" t="s">
-        <v>175</v>
+      <c r="AF10" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
@@ -4323,18 +5380,18 @@
       <c r="AN10" s="3"/>
     </row>
     <row r="11" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2">
+      <c r="A11" s="10">
         <v>7</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="I11" s="3"/>
@@ -4343,34 +5400,34 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="2" t="s">
+      <c r="S11" s="10" t="s">
         <v>62</v>
       </c>
       <c r="T11" s="3"/>
-      <c r="U11" s="2" t="s">
+      <c r="U11" s="10" t="s">
         <v>63</v>
       </c>
       <c r="V11" s="3"/>
-      <c r="W11" s="6" t="s">
+      <c r="W11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-      <c r="AB11" s="6" t="s">
+      <c r="AB11" s="2" t="s">
         <v>73</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-      <c r="AF11" s="6"/>
+      <c r="AF11" s="2"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
@@ -4381,18 +5438,18 @@
       <c r="AN11" s="3"/>
     </row>
     <row r="12" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2">
+      <c r="A12" s="10">
         <v>8</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="2" t="s">
         <v>81</v>
       </c>
       <c r="I12" s="3"/>
@@ -4401,34 +5458,34 @@
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="2" t="s">
+      <c r="O12" s="10" t="s">
         <v>78</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="2" t="s">
+      <c r="S12" s="10" t="s">
         <v>62</v>
       </c>
       <c r="T12" s="3"/>
-      <c r="U12" s="2" t="s">
+      <c r="U12" s="10" t="s">
         <v>82</v>
       </c>
       <c r="V12" s="3"/>
-      <c r="W12" s="6" t="s">
+      <c r="W12" s="2" t="s">
         <v>79</v>
       </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
-      <c r="AB12" s="6" t="s">
+      <c r="AB12" s="2" t="s">
         <v>73</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
-      <c r="AF12" s="6" t="s">
+      <c r="AF12" s="2" t="s">
         <v>83</v>
       </c>
       <c r="AG12" s="3"/>
@@ -4441,18 +5498,18 @@
       <c r="AN12" s="3"/>
     </row>
     <row r="13" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2">
+      <c r="A13" s="10">
         <v>9</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="2" t="s">
         <v>85</v>
       </c>
       <c r="I13" s="3"/>
@@ -4461,34 +5518,34 @@
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="2" t="s">
+      <c r="S13" s="10" t="s">
         <v>62</v>
       </c>
       <c r="T13" s="3"/>
-      <c r="U13" s="2" t="s">
+      <c r="U13" s="10" t="s">
         <v>63</v>
       </c>
       <c r="V13" s="3"/>
-      <c r="W13" s="6" t="s">
+      <c r="W13" s="2" t="s">
         <v>87</v>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
-      <c r="AB13" s="6" t="s">
+      <c r="AB13" s="2" t="s">
         <v>88</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
-      <c r="AF13" s="6" t="s">
+      <c r="AF13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="AG13" s="3"/>
@@ -4501,18 +5558,18 @@
       <c r="AN13" s="3"/>
     </row>
     <row r="14" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2">
+      <c r="A14" s="10">
         <v>10</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="2" t="s">
         <v>91</v>
       </c>
       <c r="I14" s="3"/>
@@ -4521,34 +5578,34 @@
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="2" t="s">
+      <c r="O14" s="10" t="s">
         <v>86</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-      <c r="S14" s="2" t="s">
+      <c r="S14" s="10" t="s">
         <v>62</v>
       </c>
       <c r="T14" s="3"/>
-      <c r="U14" s="2" t="s">
+      <c r="U14" s="10" t="s">
         <v>63</v>
       </c>
       <c r="V14" s="3"/>
-      <c r="W14" s="6" t="s">
+      <c r="W14" s="2" t="s">
         <v>92</v>
       </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
-      <c r="AB14" s="6" t="s">
+      <c r="AB14" s="2" t="s">
         <v>93</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
-      <c r="AF14" s="6" t="s">
+      <c r="AF14" s="2" t="s">
         <v>89</v>
       </c>
       <c r="AG14" s="3"/>
@@ -4561,18 +5618,18 @@
       <c r="AN14" s="3"/>
     </row>
     <row r="15" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2">
+      <c r="A15" s="10">
         <v>11</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="2" t="s">
         <v>94</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="I15" s="3"/>
@@ -4581,35 +5638,35 @@
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="2" t="s">
+      <c r="O15" s="10" t="s">
         <v>95</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-      <c r="S15" s="2" t="s">
+      <c r="S15" s="10" t="s">
         <v>51</v>
       </c>
       <c r="T15" s="3"/>
-      <c r="U15" s="2" t="s">
+      <c r="U15" s="10" t="s">
         <v>51</v>
       </c>
       <c r="V15" s="3"/>
-      <c r="W15" s="6" t="s">
+      <c r="W15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
-      <c r="AB15" s="6" t="s">
+      <c r="AB15" s="2" t="s">
         <v>51</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
-      <c r="AF15" s="6" t="s">
-        <v>176</v>
+      <c r="AF15" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
@@ -4672,6 +5729,9 @@
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AB8:AE8"/>
+    <mergeCell ref="AF9:AN9"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="O9:R9"/>
     <mergeCell ref="M2:Z2"/>
     <mergeCell ref="AF11:AN11"/>
     <mergeCell ref="S13:T13"/>
@@ -4696,9 +5756,6 @@
     <mergeCell ref="I2:L2"/>
     <mergeCell ref="AF8:AN8"/>
     <mergeCell ref="AF6:AN6"/>
-    <mergeCell ref="AF9:AN9"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="O9:R9"/>
     <mergeCell ref="H4:N4"/>
     <mergeCell ref="U12:V12"/>
     <mergeCell ref="S6:T6"/>
@@ -4763,7 +5820,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="12" t="s">
         <v>97</v>
       </c>
       <c r="B1" s="3"/>
@@ -4779,7 +5836,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -4801,7 +5858,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -4829,7 +5886,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -4851,7 +5908,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" s="2"/>
+      <c r="AE2" s="10"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -4915,375 +5972,375 @@
       <c r="AN4" s="5"/>
     </row>
     <row r="5" spans="1:40" ht="84" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2">
+      <c r="A5" s="11">
         <v>1</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="7"/>
       <c r="C5" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
       <c r="I5" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="3"/>
-      <c r="AH5" s="3"/>
-      <c r="AI5" s="2" t="s">
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="7"/>
+      <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
+      <c r="AG5" s="7"/>
+      <c r="AH5" s="7"/>
+      <c r="AI5" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
+      <c r="AJ5" s="7"/>
+      <c r="AK5" s="7"/>
+      <c r="AL5" s="7"/>
+      <c r="AM5" s="7"/>
+      <c r="AN5" s="7"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="28">
+      <c r="A6" s="11">
         <v>2</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="30" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="30" t="s">
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29"/>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="29"/>
-      <c r="AC6" s="29"/>
-      <c r="AD6" s="29"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="29"/>
-      <c r="AI6" s="28" t="s">
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+      <c r="Y6" s="7"/>
+      <c r="Z6" s="7"/>
+      <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
+      <c r="AH6" s="7"/>
+      <c r="AI6" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="AJ6" s="29"/>
-      <c r="AK6" s="29"/>
-      <c r="AL6" s="29"/>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
+      <c r="AJ6" s="7"/>
+      <c r="AK6" s="7"/>
+      <c r="AL6" s="7"/>
+      <c r="AM6" s="7"/>
+      <c r="AN6" s="7"/>
     </row>
     <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="28">
+      <c r="A7" s="11">
         <v>3</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="30" t="s">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="30" t="s">
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29"/>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="29"/>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29"/>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29"/>
-      <c r="AD7" s="29"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
-      <c r="AH7" s="29"/>
-      <c r="AI7" s="28" t="s">
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="7"/>
+      <c r="AA7" s="7"/>
+      <c r="AB7" s="7"/>
+      <c r="AC7" s="7"/>
+      <c r="AD7" s="7"/>
+      <c r="AE7" s="7"/>
+      <c r="AF7" s="7"/>
+      <c r="AG7" s="7"/>
+      <c r="AH7" s="7"/>
+      <c r="AI7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="AJ7" s="29"/>
-      <c r="AK7" s="29"/>
-      <c r="AL7" s="29"/>
-      <c r="AM7" s="29"/>
-      <c r="AN7" s="29"/>
+      <c r="AJ7" s="7"/>
+      <c r="AK7" s="7"/>
+      <c r="AL7" s="7"/>
+      <c r="AM7" s="7"/>
+      <c r="AN7" s="7"/>
     </row>
     <row r="8" spans="1:40" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="28">
+      <c r="A8" s="11">
         <v>4</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30" t="s">
+      <c r="B8" s="7"/>
+      <c r="C8" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="30" t="s">
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="30" t="s">
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+      <c r="Y8" s="7"/>
+      <c r="Z8" s="7"/>
+      <c r="AA8" s="7"/>
+      <c r="AB8" s="7"/>
+      <c r="AC8" s="7"/>
+      <c r="AD8" s="7"/>
+      <c r="AE8" s="7"/>
+      <c r="AF8" s="7"/>
+      <c r="AG8" s="7"/>
+      <c r="AH8" s="7"/>
+      <c r="AI8" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ8" s="7"/>
+      <c r="AK8" s="7"/>
+      <c r="AL8" s="7"/>
+      <c r="AM8" s="7"/>
+      <c r="AN8" s="7"/>
+    </row>
+    <row r="9" spans="1:40" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="11">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="P8" s="29"/>
-      <c r="Q8" s="29"/>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29"/>
-      <c r="Y8" s="29"/>
-      <c r="Z8" s="29"/>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="29"/>
-      <c r="AC8" s="29"/>
-      <c r="AD8" s="29"/>
-      <c r="AE8" s="29"/>
-      <c r="AF8" s="29"/>
-      <c r="AG8" s="29"/>
-      <c r="AH8" s="29"/>
-      <c r="AI8" s="28" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="7"/>
+      <c r="AA9" s="7"/>
+      <c r="AB9" s="7"/>
+      <c r="AC9" s="7"/>
+      <c r="AD9" s="7"/>
+      <c r="AE9" s="7"/>
+      <c r="AF9" s="7"/>
+      <c r="AG9" s="7"/>
+      <c r="AH9" s="7"/>
+      <c r="AI9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="AJ8" s="29"/>
-      <c r="AK8" s="29"/>
-      <c r="AL8" s="29"/>
-      <c r="AM8" s="29"/>
-      <c r="AN8" s="29"/>
-    </row>
-    <row r="9" spans="1:40" ht="36" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="28">
-        <v>5</v>
-      </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="30" t="s">
+      <c r="AJ9" s="7"/>
+      <c r="AK9" s="7"/>
+      <c r="AL9" s="7"/>
+      <c r="AM9" s="7"/>
+      <c r="AN9" s="7"/>
+    </row>
+    <row r="10" spans="1:40" ht="84" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="11">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7"/>
+      <c r="C10" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+      <c r="Y10" s="7"/>
+      <c r="Z10" s="7"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="7"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="7"/>
+      <c r="AH10" s="7"/>
+      <c r="AI10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ10" s="7"/>
+      <c r="AK10" s="7"/>
+      <c r="AL10" s="7"/>
+      <c r="AM10" s="7"/>
+      <c r="AN10" s="7"/>
+    </row>
+    <row r="11" spans="1:40" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="11">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7"/>
+      <c r="C11" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="P9" s="29"/>
-      <c r="Q9" s="29"/>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29"/>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29"/>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29"/>
-      <c r="AA9" s="29"/>
-      <c r="AB9" s="29"/>
-      <c r="AC9" s="29"/>
-      <c r="AD9" s="29"/>
-      <c r="AE9" s="29"/>
-      <c r="AF9" s="29"/>
-      <c r="AG9" s="29"/>
-      <c r="AH9" s="29"/>
-      <c r="AI9" s="28" t="s">
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="7"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="AJ9" s="29"/>
-      <c r="AK9" s="29"/>
-      <c r="AL9" s="29"/>
-      <c r="AM9" s="29"/>
-      <c r="AN9" s="29"/>
-    </row>
-    <row r="10" spans="1:40" ht="84" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="28">
-        <v>6</v>
-      </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30" t="s">
-        <v>110</v>
-      </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="P10" s="29"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29"/>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29"/>
-      <c r="AA10" s="29"/>
-      <c r="AB10" s="29"/>
-      <c r="AC10" s="29"/>
-      <c r="AD10" s="29"/>
-      <c r="AE10" s="29"/>
-      <c r="AF10" s="29"/>
-      <c r="AG10" s="29"/>
-      <c r="AH10" s="29"/>
-      <c r="AI10" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ10" s="29"/>
-      <c r="AK10" s="29"/>
-      <c r="AL10" s="29"/>
-      <c r="AM10" s="29"/>
-      <c r="AN10" s="29"/>
-    </row>
-    <row r="11" spans="1:40" ht="69.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="28">
-        <v>7</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="30" t="s">
-        <v>169</v>
-      </c>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
-      <c r="AB11" s="29"/>
-      <c r="AC11" s="29"/>
-      <c r="AD11" s="29"/>
-      <c r="AE11" s="29"/>
-      <c r="AF11" s="29"/>
-      <c r="AG11" s="29"/>
-      <c r="AH11" s="29"/>
-      <c r="AI11" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ11" s="29"/>
-      <c r="AK11" s="29"/>
-      <c r="AL11" s="29"/>
-      <c r="AM11" s="29"/>
-      <c r="AN11" s="29"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7"/>
+      <c r="AL11" s="7"/>
+      <c r="AM11" s="7"/>
+      <c r="AN11" s="7"/>
     </row>
     <row r="12" spans="1:40" ht="140.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2">
+      <c r="A12" s="10">
         <v>8</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="2" t="s">
         <v>113</v>
       </c>
       <c r="D12" s="3"/>
@@ -5291,16 +6348,16 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="6" t="s">
-        <v>114</v>
+      <c r="I12" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="6" t="s">
-        <v>170</v>
+      <c r="O12" s="2" t="s">
+        <v>215</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -5321,8 +6378,8 @@
       <c r="AF12" s="3"/>
       <c r="AG12" s="3"/>
       <c r="AH12" s="3"/>
-      <c r="AI12" s="2" t="s">
-        <v>115</v>
+      <c r="AI12" s="10" t="s">
+        <v>114</v>
       </c>
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
@@ -5331,28 +6388,28 @@
       <c r="AN12" s="3"/>
     </row>
     <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2">
+      <c r="A13" s="10">
         <v>9</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="6" t="s">
-        <v>116</v>
+      <c r="C13" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="6" t="s">
-        <v>117</v>
+      <c r="I13" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
-      <c r="O13" s="6" t="s">
-        <v>118</v>
+      <c r="O13" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
@@ -5373,7 +6430,7 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
       <c r="AH13" s="3"/>
-      <c r="AI13" s="2" t="s">
+      <c r="AI13" s="10" t="s">
         <v>20</v>
       </c>
       <c r="AJ13" s="3"/>
@@ -5462,8 +6519,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>187</v>
+      <c r="A1" s="12" t="s">
+        <v>184</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5478,7 +6535,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -5500,7 +6557,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -5528,7 +6585,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -5550,7 +6607,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" s="2"/>
+      <c r="AE2" s="10"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -5562,194 +6619,194 @@
       <c r="AN2" s="3"/>
     </row>
     <row r="4" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="26" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="D4" s="31"/>
+      <c r="E4" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="K4" s="29"/>
+      <c r="L4" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="23" t="s">
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="23" t="s">
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="27" t="s">
         <v>190</v>
       </c>
-      <c r="K4" s="25"/>
-      <c r="L4" s="23" t="s">
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="23" t="s">
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="25"/>
-      <c r="U4" s="23" t="s">
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="24"/>
-      <c r="Z4" s="25"/>
-      <c r="AA4" s="23" t="s">
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="29"/>
+    </row>
+    <row r="5" spans="1:40" ht="62.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="22">
+        <v>1</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="25"/>
-      <c r="AF4" s="23" t="s">
+      <c r="D5" s="23"/>
+      <c r="E5" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="AG4" s="24"/>
-      <c r="AH4" s="24"/>
-      <c r="AI4" s="24"/>
-      <c r="AJ4" s="25"/>
-      <c r="AK4" s="23" t="s">
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="24" t="s">
         <v>196</v>
       </c>
-      <c r="AL4" s="24"/>
-      <c r="AM4" s="24"/>
-      <c r="AN4" s="25"/>
-    </row>
-    <row r="5" spans="1:40" ht="62.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="18">
-        <v>1</v>
-      </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="18" t="s">
+      <c r="K5" s="26"/>
+      <c r="L5" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="D5" s="19"/>
-      <c r="E5" s="20" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="22"/>
-      <c r="J5" s="20" t="s">
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="K5" s="22"/>
-      <c r="L5" s="15" t="s">
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="17"/>
-      <c r="Q5" s="15" t="s">
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="17"/>
-      <c r="U5" s="15" t="s">
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
+      <c r="AI5" s="20"/>
+      <c r="AJ5" s="21"/>
+      <c r="AK5" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="17"/>
-      <c r="AA5" s="15" t="s">
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="21"/>
+    </row>
+    <row r="6" spans="1:40" ht="104.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="22">
+        <v>2</v>
+      </c>
+      <c r="B6" s="23"/>
+      <c r="C6" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="AB5" s="16"/>
-      <c r="AC5" s="16"/>
-      <c r="AD5" s="16"/>
-      <c r="AE5" s="17"/>
-      <c r="AF5" s="15" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="24" t="s">
+        <v>196</v>
+      </c>
+      <c r="K6" s="26"/>
+      <c r="L6" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="AG5" s="16"/>
-      <c r="AH5" s="16"/>
-      <c r="AI5" s="16"/>
-      <c r="AJ5" s="17"/>
-      <c r="AK5" s="15" t="s">
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="AL5" s="16"/>
-      <c r="AM5" s="16"/>
-      <c r="AN5" s="17"/>
-    </row>
-    <row r="6" spans="1:40" ht="104.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="18">
-        <v>2</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="20" t="s">
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="K6" s="22"/>
-      <c r="L6" s="15" t="s">
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="15" t="s">
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="21"/>
+      <c r="AF6" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="17"/>
-      <c r="U6" s="15" t="s">
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
+      <c r="AI6" s="20"/>
+      <c r="AJ6" s="21"/>
+      <c r="AK6" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="17"/>
-      <c r="AA6" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="AB6" s="16"/>
-      <c r="AC6" s="16"/>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="17"/>
-      <c r="AF6" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="AG6" s="16"/>
-      <c r="AH6" s="16"/>
-      <c r="AI6" s="16"/>
-      <c r="AJ6" s="17"/>
-      <c r="AK6" s="15" t="s">
-        <v>212</v>
-      </c>
-      <c r="AL6" s="16"/>
-      <c r="AM6" s="16"/>
-      <c r="AN6" s="17"/>
+      <c r="AL6" s="20"/>
+      <c r="AM6" s="20"/>
+      <c r="AN6" s="21"/>
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -5801,19 +6858,19 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0C884DA-2BA7-4F59-892F-88C842290283}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN18"/>
+  <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>119</v>
+      <c r="A1" s="12" t="s">
+        <v>217</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5828,7 +6885,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
       <c r="L1" s="5"/>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="N1" s="3"/>
@@ -5850,7 +6907,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
       <c r="AD1" s="5"/>
-      <c r="AE1" s="2" t="s">
+      <c r="AE1" s="10" t="s">
         <v>6</v>
       </c>
       <c r="AF1" s="3"/>
@@ -5878,7 +6935,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="N2" s="3"/>
@@ -5900,7 +6957,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
-      <c r="AE2" s="2"/>
+      <c r="AE2" s="10"/>
       <c r="AF2" s="3"/>
       <c r="AG2" s="3"/>
       <c r="AH2" s="3"/>
@@ -5911,13 +6968,363 @@
       <c r="AM2" s="3"/>
       <c r="AN2" s="3"/>
     </row>
+    <row r="4" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="30" t="s">
+        <v>226</v>
+      </c>
+      <c r="B4" s="31"/>
+      <c r="C4" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="D4" s="31"/>
+      <c r="E4" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="K4" s="29"/>
+      <c r="L4" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="27" t="s">
+        <v>224</v>
+      </c>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="29"/>
+      <c r="AA4" s="27" t="s">
+        <v>222</v>
+      </c>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="29"/>
+      <c r="AF4" s="27" t="s">
+        <v>218</v>
+      </c>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="29"/>
+      <c r="AK4" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="29"/>
+    </row>
+    <row r="5" spans="1:40" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="22">
+        <v>1</v>
+      </c>
+      <c r="B5" s="23"/>
+      <c r="C5" s="22" t="s">
+        <v>228</v>
+      </c>
+      <c r="D5" s="23"/>
+      <c r="E5" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="24" t="s">
+        <v>231</v>
+      </c>
+      <c r="K5" s="26"/>
+      <c r="L5" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="21"/>
+      <c r="Q5" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="21"/>
+      <c r="U5" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="21"/>
+      <c r="AA5" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB5" s="20"/>
+      <c r="AC5" s="20"/>
+      <c r="AD5" s="20"/>
+      <c r="AE5" s="21"/>
+      <c r="AF5" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="20"/>
+      <c r="AI5" s="20"/>
+      <c r="AJ5" s="21"/>
+      <c r="AK5" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="AL5" s="20"/>
+      <c r="AM5" s="20"/>
+      <c r="AN5" s="21"/>
+    </row>
+    <row r="6" spans="1:40" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="22">
+        <v>2</v>
+      </c>
+      <c r="B6" s="23"/>
+      <c r="C6" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="D6" s="23"/>
+      <c r="E6" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="K6" s="26"/>
+      <c r="L6" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="21"/>
+      <c r="Q6" s="19" t="s">
+        <v>243</v>
+      </c>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="21"/>
+      <c r="U6" s="19" t="s">
+        <v>241</v>
+      </c>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="21"/>
+      <c r="AA6" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="AB6" s="20"/>
+      <c r="AC6" s="20"/>
+      <c r="AD6" s="20"/>
+      <c r="AE6" s="21"/>
+      <c r="AF6" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="20"/>
+      <c r="AI6" s="20"/>
+      <c r="AJ6" s="21"/>
+      <c r="AK6" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="AL6" s="20"/>
+      <c r="AM6" s="20"/>
+      <c r="AN6" s="21"/>
+    </row>
+    <row r="8" spans="1:40" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="U6:Z6"/>
+    <mergeCell ref="AA6:AE6"/>
+    <mergeCell ref="AF6:AJ6"/>
+    <mergeCell ref="AK6:AN6"/>
+    <mergeCell ref="U5:Z5"/>
+    <mergeCell ref="AA5:AE5"/>
+    <mergeCell ref="AF5:AJ5"/>
+    <mergeCell ref="AK5:AN5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="L6:P6"/>
+    <mergeCell ref="Q6:T6"/>
+    <mergeCell ref="U4:Z4"/>
+    <mergeCell ref="AA4:AE4"/>
+    <mergeCell ref="AF4:AJ4"/>
+    <mergeCell ref="AK4:AN4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:P5"/>
+    <mergeCell ref="Q5:T5"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:P4"/>
+    <mergeCell ref="Q4:T4"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="M1:Z1"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="AE1:AN1"/>
+    <mergeCell ref="I2:L2"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="AA2:AD2"/>
+    <mergeCell ref="AE2:AN2"/>
+  </mergeCells>
+  <phoneticPr fontId="8"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AN18"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="40" width="3.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
+      <c r="AE1" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="AF1" s="3"/>
+      <c r="AG1" s="3"/>
+      <c r="AH1" s="3"/>
+      <c r="AI1" s="3"/>
+      <c r="AJ1" s="3"/>
+      <c r="AK1" s="3"/>
+      <c r="AL1" s="3"/>
+      <c r="AM1" s="3"/>
+      <c r="AN1" s="3"/>
+    </row>
+    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="3"/>
+      <c r="V2" s="3"/>
+      <c r="W2" s="3"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" s="5"/>
+      <c r="AC2" s="5"/>
+      <c r="AD2" s="5"/>
+      <c r="AE2" s="10"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+    </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -5925,7 +7332,7 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
@@ -5943,19 +7350,19 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z4" s="5"/>
       <c r="AA4" s="5"/>
       <c r="AB4" s="5"/>
       <c r="AC4" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
       <c r="AF4" s="5"/>
       <c r="AG4" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AH4" s="5"/>
       <c r="AI4" s="5"/>
@@ -5968,11 +7375,11 @@
       <c r="AN4" s="5"/>
     </row>
     <row r="5" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2">
+      <c r="A5" s="10">
         <v>1</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D5" s="3"/>
@@ -5980,8 +7387,8 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="6" t="s">
-        <v>125</v>
+      <c r="I5" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
@@ -5998,35 +7405,35 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
-      <c r="Y5" s="2" t="s">
+      <c r="Y5" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
-      <c r="AC5" s="2" t="s">
+      <c r="AC5" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3"/>
       <c r="AF5" s="3"/>
-      <c r="AG5" s="2" t="s">
-        <v>126</v>
+      <c r="AG5" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="AH5" s="3"/>
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
-      <c r="AK5" s="6"/>
+      <c r="AK5" s="2"/>
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
       <c r="AN5" s="3"/>
     </row>
     <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
+      <c r="A6" s="10">
         <v>2</v>
       </c>
       <c r="B6" s="3"/>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D6" s="3"/>
@@ -6034,8 +7441,8 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="6" t="s">
-        <v>127</v>
+      <c r="I6" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -6052,35 +7459,35 @@
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
-      <c r="Y6" s="2" t="s">
+      <c r="Y6" s="10" t="s">
         <v>51</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
-      <c r="AC6" s="2" t="s">
+      <c r="AC6" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3"/>
       <c r="AF6" s="3"/>
-      <c r="AG6" s="2" t="s">
-        <v>128</v>
+      <c r="AG6" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="AH6" s="3"/>
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
-      <c r="AK6" s="6"/>
+      <c r="AK6" s="2"/>
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
       <c r="AN6" s="3"/>
     </row>
     <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="2">
+      <c r="A7" s="10">
         <v>3</v>
       </c>
       <c r="B7" s="3"/>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D7" s="3"/>
@@ -6088,8 +7495,8 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="6" t="s">
-        <v>125</v>
+      <c r="I7" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -6106,35 +7513,35 @@
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
-      <c r="Y7" s="2" t="s">
+      <c r="Y7" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
-      <c r="AC7" s="2" t="s">
+      <c r="AC7" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3"/>
       <c r="AF7" s="3"/>
-      <c r="AG7" s="2" t="s">
-        <v>126</v>
+      <c r="AG7" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="AH7" s="3"/>
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
-      <c r="AK7" s="6"/>
+      <c r="AK7" s="2"/>
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
       <c r="AN7" s="3"/>
     </row>
     <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2">
+      <c r="A8" s="10">
         <v>4</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="3"/>
@@ -6142,8 +7549,8 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="6" t="s">
-        <v>127</v>
+      <c r="I8" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -6160,44 +7567,44 @@
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
-      <c r="Y8" s="2" t="s">
+      <c r="Y8" s="10" t="s">
         <v>51</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
-      <c r="AC8" s="2" t="s">
+      <c r="AC8" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
       <c r="AF8" s="3"/>
-      <c r="AG8" s="2" t="s">
-        <v>128</v>
+      <c r="AG8" s="10" t="s">
+        <v>127</v>
       </c>
       <c r="AH8" s="3"/>
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
-      <c r="AK8" s="6"/>
+      <c r="AK8" s="2"/>
       <c r="AL8" s="3"/>
       <c r="AM8" s="3"/>
       <c r="AN8" s="3"/>
     </row>
     <row r="9" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2">
+      <c r="A9" s="10">
         <v>5</v>
       </c>
       <c r="B9" s="3"/>
-      <c r="C9" s="6" t="s">
-        <v>129</v>
+      <c r="C9" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="6" t="s">
-        <v>130</v>
+      <c r="I9" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -6214,37 +7621,37 @@
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
-      <c r="Y9" s="2" t="s">
+      <c r="Y9" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
-      <c r="AC9" s="2" t="s">
+      <c r="AC9" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
-      <c r="AG9" s="2" t="s">
-        <v>131</v>
+      <c r="AG9" s="10" t="s">
+        <v>130</v>
       </c>
       <c r="AH9" s="3"/>
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
-      <c r="AK9" s="6" t="s">
-        <v>132</v>
+      <c r="AK9" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="AL9" s="3"/>
       <c r="AM9" s="3"/>
       <c r="AN9" s="3"/>
     </row>
     <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2">
+      <c r="A10" s="10">
         <v>6</v>
       </c>
       <c r="B10" s="3"/>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D10" s="3"/>
@@ -6252,8 +7659,8 @@
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="6" t="s">
-        <v>125</v>
+      <c r="I10" s="2" t="s">
+        <v>124</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -6270,35 +7677,35 @@
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
-      <c r="Y10" s="2" t="s">
+      <c r="Y10" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
-      <c r="AC10" s="2" t="s">
+      <c r="AC10" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3"/>
       <c r="AF10" s="3"/>
-      <c r="AG10" s="2" t="s">
-        <v>126</v>
+      <c r="AG10" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="AH10" s="3"/>
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
-      <c r="AK10" s="6"/>
+      <c r="AK10" s="2"/>
       <c r="AL10" s="3"/>
       <c r="AM10" s="3"/>
       <c r="AN10" s="3"/>
     </row>
     <row r="11" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2">
+      <c r="A11" s="10">
         <v>7</v>
       </c>
       <c r="B11" s="3"/>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="3"/>
@@ -6306,8 +7713,8 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="6" t="s">
-        <v>133</v>
+      <c r="I11" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -6324,35 +7731,35 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-      <c r="Y11" s="2" t="s">
+      <c r="Y11" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-      <c r="AC11" s="2" t="s">
+      <c r="AC11" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-      <c r="AG11" s="2" t="s">
-        <v>134</v>
+      <c r="AG11" s="10" t="s">
+        <v>133</v>
       </c>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
-      <c r="AK11" s="6"/>
+      <c r="AK11" s="2"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
     </row>
     <row r="12" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2">
+      <c r="A12" s="10">
         <v>8</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D12" s="3"/>
@@ -6360,8 +7767,8 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="6" t="s">
-        <v>135</v>
+      <c r="I12" s="2" t="s">
+        <v>134</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -6378,35 +7785,35 @@
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
-      <c r="Y12" s="2" t="s">
+      <c r="Y12" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
-      <c r="AC12" s="2" t="s">
+      <c r="AC12" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD12" s="3"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
-      <c r="AG12" s="2" t="s">
-        <v>126</v>
+      <c r="AG12" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="AH12" s="3"/>
       <c r="AI12" s="3"/>
       <c r="AJ12" s="3"/>
-      <c r="AK12" s="6"/>
+      <c r="AK12" s="2"/>
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
       <c r="AN12" s="3"/>
     </row>
     <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2">
+      <c r="A13" s="10">
         <v>9</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D13" s="3"/>
@@ -6414,8 +7821,8 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="6" t="s">
-        <v>136</v>
+      <c r="I13" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -6432,37 +7839,37 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
-      <c r="Y13" s="2" t="s">
+      <c r="Y13" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
-      <c r="AC13" s="2" t="s">
+      <c r="AC13" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3"/>
       <c r="AF13" s="3"/>
-      <c r="AG13" s="2" t="s">
-        <v>137</v>
+      <c r="AG13" s="10" t="s">
+        <v>136</v>
       </c>
       <c r="AH13" s="3"/>
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
-      <c r="AK13" s="6" t="s">
-        <v>132</v>
+      <c r="AK13" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
       <c r="AN13" s="3"/>
     </row>
     <row r="14" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2">
+      <c r="A14" s="10">
         <v>10</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D14" s="3"/>
@@ -6470,8 +7877,8 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="6" t="s">
-        <v>138</v>
+      <c r="I14" s="2" t="s">
+        <v>137</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -6488,35 +7895,35 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
-      <c r="Y14" s="2" t="s">
+      <c r="Y14" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
-      <c r="AC14" s="2" t="s">
+      <c r="AC14" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3"/>
       <c r="AF14" s="3"/>
-      <c r="AG14" s="2" t="s">
-        <v>139</v>
+      <c r="AG14" s="10" t="s">
+        <v>138</v>
       </c>
       <c r="AH14" s="3"/>
       <c r="AI14" s="3"/>
       <c r="AJ14" s="3"/>
-      <c r="AK14" s="6"/>
+      <c r="AK14" s="2"/>
       <c r="AL14" s="3"/>
       <c r="AM14" s="3"/>
       <c r="AN14" s="3"/>
     </row>
     <row r="15" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="2">
+      <c r="A15" s="10">
         <v>11</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="2" t="s">
         <v>90</v>
       </c>
       <c r="D15" s="3"/>
@@ -6524,8 +7931,8 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="6" t="s">
-        <v>140</v>
+      <c r="I15" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
@@ -6542,46 +7949,46 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
-      <c r="Y15" s="2" t="s">
+      <c r="Y15" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
-      <c r="AC15" s="2" t="s">
+      <c r="AC15" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3"/>
       <c r="AF15" s="3"/>
-      <c r="AG15" s="2" t="s">
-        <v>141</v>
+      <c r="AG15" s="10" t="s">
+        <v>140</v>
       </c>
       <c r="AH15" s="3"/>
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
-      <c r="AK15" s="6" t="s">
-        <v>132</v>
+      <c r="AK15" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="AL15" s="3"/>
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
     </row>
     <row r="16" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="2">
+      <c r="A16" s="10">
         <v>12</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="6" t="s">
-        <v>142</v>
+      <c r="C16" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
-      <c r="I16" s="6" t="s">
-        <v>143</v>
+      <c r="I16" s="2" t="s">
+        <v>142</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
@@ -6598,26 +8005,26 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-      <c r="Y16" s="2" t="s">
+      <c r="Y16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-      <c r="AC16" s="2" t="s">
+      <c r="AC16" s="10" t="s">
         <v>63</v>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-      <c r="AG16" s="2" t="s">
-        <v>144</v>
+      <c r="AG16" s="10" t="s">
+        <v>143</v>
       </c>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
-      <c r="AK16" s="6" t="s">
-        <v>132</v>
+      <c r="AK16" s="2" t="s">
+        <v>131</v>
       </c>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
@@ -6625,7 +8032,7 @@
     </row>
     <row r="18" spans="1:1" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -6641,6 +8048,11 @@
     <mergeCell ref="Y5:AB5"/>
     <mergeCell ref="I4:X4"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="M2:Z2"/>
+    <mergeCell ref="I9:X9"/>
+    <mergeCell ref="I11:X11"/>
+    <mergeCell ref="AK4:AN4"/>
+    <mergeCell ref="AE2:AN2"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="AG8:AJ8"/>
     <mergeCell ref="AC7:AF7"/>
@@ -6673,13 +8085,6 @@
     <mergeCell ref="AK5:AN5"/>
     <mergeCell ref="AK11:AN11"/>
     <mergeCell ref="Y6:AB6"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="I9:X9"/>
-    <mergeCell ref="I11:X11"/>
-    <mergeCell ref="AK4:AN4"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="AG7:AJ7"/>
-    <mergeCell ref="Y7:AB7"/>
     <mergeCell ref="AK10:AN10"/>
     <mergeCell ref="Y8:AB8"/>
     <mergeCell ref="I2:L2"/>
@@ -6730,717 +8135,8 @@
     <mergeCell ref="AC5:AF5"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C12:H12"/>
-  </mergeCells>
-  <phoneticPr fontId="8"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AN14"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="40" width="3.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB1" s="5"/>
-      <c r="AC1" s="5"/>
-      <c r="AD1" s="5"/>
-      <c r="AE1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="AF1" s="3"/>
-      <c r="AG1" s="3"/>
-      <c r="AH1" s="3"/>
-      <c r="AI1" s="3"/>
-      <c r="AJ1" s="3"/>
-      <c r="AK1" s="3"/>
-      <c r="AL1" s="3"/>
-      <c r="AM1" s="3"/>
-      <c r="AN1" s="3"/>
-    </row>
-    <row r="2" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
-    </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.15">
-      <c r="A4" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="5"/>
-      <c r="AD4" s="5"/>
-      <c r="AE4" s="5"/>
-      <c r="AF4" s="5"/>
-      <c r="AG4" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="AH4" s="5"/>
-      <c r="AI4" s="5"/>
-      <c r="AJ4" s="5"/>
-      <c r="AK4" s="5"/>
-      <c r="AL4" s="5"/>
-      <c r="AM4" s="5"/>
-      <c r="AN4" s="5"/>
-    </row>
-    <row r="5" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
-      <c r="S5" s="3"/>
-      <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-      <c r="AB5" s="3"/>
-      <c r="AC5" s="3"/>
-      <c r="AD5" s="3"/>
-      <c r="AE5" s="3"/>
-      <c r="AF5" s="3"/>
-      <c r="AG5" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="AH5" s="3"/>
-      <c r="AI5" s="3"/>
-      <c r="AJ5" s="3"/>
-      <c r="AK5" s="3"/>
-      <c r="AL5" s="3"/>
-      <c r="AM5" s="3"/>
-      <c r="AN5" s="3"/>
-    </row>
-    <row r="6" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3"/>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="3"/>
-    </row>
-    <row r="7" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
-      <c r="S7" s="3"/>
-      <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-      <c r="AA7" s="3"/>
-      <c r="AB7" s="3"/>
-      <c r="AC7" s="3"/>
-      <c r="AD7" s="3"/>
-      <c r="AE7" s="3"/>
-      <c r="AF7" s="3"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="3"/>
-      <c r="AI7" s="3"/>
-      <c r="AJ7" s="3"/>
-      <c r="AK7" s="3"/>
-      <c r="AL7" s="3"/>
-      <c r="AM7" s="3"/>
-      <c r="AN7" s="3"/>
-    </row>
-    <row r="8" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="3"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AD8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="6"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="3"/>
-      <c r="AJ8" s="3"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="3"/>
-      <c r="AN8" s="3"/>
-    </row>
-    <row r="9" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="3"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AD9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="3"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="3"/>
-      <c r="AN9" s="3"/>
-    </row>
-    <row r="10" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="3"/>
-      <c r="AC10" s="3"/>
-      <c r="AD10" s="3"/>
-      <c r="AE10" s="3"/>
-      <c r="AF10" s="3"/>
-      <c r="AG10" s="6"/>
-      <c r="AH10" s="3"/>
-      <c r="AI10" s="3"/>
-      <c r="AJ10" s="3"/>
-      <c r="AK10" s="3"/>
-      <c r="AL10" s="3"/>
-      <c r="AM10" s="3"/>
-      <c r="AN10" s="3"/>
-    </row>
-    <row r="11" spans="1:40" ht="27.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-      <c r="AA11" s="3"/>
-      <c r="AB11" s="3"/>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
-      <c r="AE11" s="3"/>
-      <c r="AF11" s="3"/>
-      <c r="AG11" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="AH11" s="3"/>
-      <c r="AI11" s="3"/>
-      <c r="AJ11" s="3"/>
-      <c r="AK11" s="3"/>
-      <c r="AL11" s="3"/>
-      <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-    </row>
-    <row r="12" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-    </row>
-    <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-    </row>
-    <row r="14" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="6"/>
-      <c r="AH14" s="3"/>
-      <c r="AI14" s="3"/>
-      <c r="AJ14" s="3"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="3"/>
-      <c r="AM14" s="3"/>
-      <c r="AN14" s="3"/>
-    </row>
-  </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="A13:E13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="I13:AF13"/>
-    <mergeCell ref="AG13:AN13"/>
-    <mergeCell ref="A14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:AF14"/>
-    <mergeCell ref="AG14:AN14"/>
-    <mergeCell ref="AG12:AN12"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="I6:AF6"/>
-    <mergeCell ref="I11:AF11"/>
-    <mergeCell ref="F12:H12"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="AG8:AN8"/>
-    <mergeCell ref="I12:AF12"/>
-    <mergeCell ref="AG6:AN6"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="I7:AF7"/>
-    <mergeCell ref="AG10:AN10"/>
-    <mergeCell ref="F8:H8"/>
-    <mergeCell ref="M2:Z2"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="AG11:AN11"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="I2:L2"/>
-    <mergeCell ref="I5:AF5"/>
-    <mergeCell ref="I8:AF8"/>
-    <mergeCell ref="I4:AF4"/>
-    <mergeCell ref="AG7:AN7"/>
-    <mergeCell ref="I10:AF10"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="AA2:AD2"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="AG9:AN9"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="F11:H11"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="I9:AF9"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="AG5:AN5"/>
-    <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="AG4:AN4"/>
+    <mergeCell ref="AG7:AJ7"/>
+    <mergeCell ref="Y7:AB7"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/doc/excel/화면설계서_X1_항공편검색.xlsx
+++ b/doc/excel/화면설계서_X1_항공편검색.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\gwx\java\SpringLab01\doc\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD0FA9B1-AAE5-4ADB-8246-C1368D28E6AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AAC743-572D-43B3-ACBC-24790D55745E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="표지" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="249">
   <si>
     <t>HOSHIMOTO AIR 항공권 예약 시스템</t>
   </si>
@@ -571,10 +571,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>GET /api/flights?tripType=…&amp;departureAirport=…&amp;arrivalAirport=…&amp;departureDate=…&amp;returnDate=…&amp;adultCount=…&amp;infantCount=…（1단계는 departureAirport·arrivalAirport만）</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>E009</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -675,10 +671,6 @@
   </si>
   <si>
     <t>/api/flights</t>
-  </si>
-  <si>
-    <t>이벤트정의 No.8
-(검색)</t>
   </si>
   <si>
     <t>1단계:
@@ -1295,72 +1287,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <r>
-      <t>1. 입력 체크(클라이언트)를 수행한다. 에러 시 메시지를 표시하고 처리를 중단한다.
-2. 검색 조건을 쿼리 파라미터로 하여 GET /api/flights 를 전송한다.
-　※ 1단계는 출발지·도착지만 전송한다.(specs X1 참조)
-3. 입력 체크(서버)를 수행한다.
-　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에러 있음: 화면을 이동하지 않고, 입력값을 유지한 채 에러 메시지를 표시한다.
-　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>에러 없음: X2 항공편 목록을 표시한다.
-　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Malgun Gothic"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>결과 0건: X2에 I001을 표시한다.</t>
-    </r>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>frontend/src/features/home/components/X1_FlightSearchBar.tsx
 （공통 부품: C1_AirportSelect.tsx, 「사용컴포넌트」 시트 참조）</t>
     <phoneticPr fontId="8"/>
@@ -1488,12 +1414,36 @@
     <t>템플릿에 X1_FlightSearchBar.tsx 기입, 사용컴포넌트 시트 신규 추가(X1_FlightSearchBar, C1_AirportSelect)</t>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>X2로 이동: GET /flights?departureAirport=…&amp;arrivalAirport=…（1단계는 departureAirport·arrivalAirport만. X1은 API를 호출하지 않는다）</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1. 입력 체크(클라이언트)를 수행한다. 에러 시 메시지를 표시하고 처리를 중단한다.
+2. 검색 조건을 쿼리 파라미터로 하여 X2(/flights?…)로 이동한다.
+　※ 1단계는 출발지·도착지만 넘긴다.(specs X1·X2 참조)
+　※ 항공편 검색 API 호출·결과 0건(I001)·서버 에러 표시는 X2에서 한다.(X2 이벤트정의 No.1 참조)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>X1에서는 호출하지 않음
+(X2 이벤트정의 No.1에서 호출)</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>화면개요, 이벤트정의, 사용API</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>검색 시 API를 호출하지 않고 X2로 이동하도록 변경(검색 API 호출·0건·서버 에러 표시는 X2로 이동)</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1588,12 +1538,6 @@
       <name val="Malgun Gothic"/>
       <family val="2"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="6">
@@ -3167,19 +3111,19 @@
     </row>
     <row r="13" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
@@ -3215,19 +3159,19 @@
     </row>
     <row r="14" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
@@ -3328,7 +3272,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="40" width="3.25" customWidth="1"/>
@@ -3550,7 +3494,7 @@
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
@@ -3560,7 +3504,7 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
@@ -3600,7 +3544,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
@@ -3610,7 +3554,7 @@
       <c r="O7" s="3"/>
       <c r="P7" s="3"/>
       <c r="Q7" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
@@ -3650,7 +3594,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -3660,7 +3604,7 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
@@ -3687,15 +3631,21 @@
       <c r="AN8" s="3"/>
     </row>
     <row r="9" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10"/>
+      <c r="A9" s="10">
+        <v>1.4</v>
+      </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
-      <c r="D9" s="10"/>
+      <c r="D9" s="18">
+        <v>46311</v>
+      </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -3703,7 +3653,9 @@
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
-      <c r="Q9" s="2"/>
+      <c r="Q9" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
@@ -3980,42 +3932,89 @@
       <c r="AM15" s="3"/>
       <c r="AN15" s="3"/>
     </row>
+    <row r="16" spans="1:40" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="10"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="10"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="74">
     <mergeCell ref="AI8:AN8"/>
-    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I9:P9"/>
+    <mergeCell ref="Q9:AH9"/>
+    <mergeCell ref="AI9:AN9"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="Q16:AH16"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="I14:P14"/>
     <mergeCell ref="A15:C15"/>
-    <mergeCell ref="Q15:AH15"/>
-    <mergeCell ref="I1:L1"/>
-    <mergeCell ref="I13:P13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="Q12:AH12"/>
-    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="Q13:AH13"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="D4:H4"/>
     <mergeCell ref="I5:P5"/>
-    <mergeCell ref="Q10:AH10"/>
+    <mergeCell ref="Q11:AH11"/>
     <mergeCell ref="I2:L2"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A12:C12"/>
     <mergeCell ref="D7:H7"/>
     <mergeCell ref="A1:H2"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="I14:P14"/>
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="I15:P15"/>
+    <mergeCell ref="A14:C14"/>
     <mergeCell ref="Q4:AH4"/>
     <mergeCell ref="M1:Z1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D13:H13"/>
     <mergeCell ref="AA1:AD1"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="Q9:AH9"/>
+    <mergeCell ref="Q10:AH10"/>
     <mergeCell ref="AE1:AN1"/>
-    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
     <mergeCell ref="Q7:AH7"/>
-    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="D10:H10"/>
     <mergeCell ref="I4:P4"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="Q13:AH13"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="Q14:AH14"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="A5:C5"/>
@@ -4024,33 +4023,33 @@
     <mergeCell ref="I7:P7"/>
     <mergeCell ref="AA2:AD2"/>
     <mergeCell ref="D5:H5"/>
-    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="D11:H11"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="I8:P8"/>
     <mergeCell ref="Q8:AH8"/>
+    <mergeCell ref="AI13:AN13"/>
+    <mergeCell ref="Q12:AH12"/>
+    <mergeCell ref="I13:P13"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="I11:P11"/>
+    <mergeCell ref="I12:P12"/>
+    <mergeCell ref="AI16:AN16"/>
+    <mergeCell ref="AI15:AN15"/>
+    <mergeCell ref="I10:P10"/>
+    <mergeCell ref="AE2:AN2"/>
+    <mergeCell ref="Q15:AH15"/>
     <mergeCell ref="AI12:AN12"/>
-    <mergeCell ref="Q11:AH11"/>
-    <mergeCell ref="I12:P12"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="I10:P10"/>
-    <mergeCell ref="I11:P11"/>
-    <mergeCell ref="AI15:AN15"/>
-    <mergeCell ref="AI14:AN14"/>
-    <mergeCell ref="I9:P9"/>
-    <mergeCell ref="AE2:AN2"/>
-    <mergeCell ref="Q14:AH14"/>
-    <mergeCell ref="AI11:AN11"/>
     <mergeCell ref="AI6:AN6"/>
     <mergeCell ref="I6:P6"/>
     <mergeCell ref="Q5:AH5"/>
+    <mergeCell ref="AI11:AN11"/>
+    <mergeCell ref="AI14:AN14"/>
+    <mergeCell ref="AI5:AN5"/>
     <mergeCell ref="AI10:AN10"/>
-    <mergeCell ref="AI13:AN13"/>
-    <mergeCell ref="AI5:AN5"/>
-    <mergeCell ref="AI9:AN9"/>
     <mergeCell ref="AI7:AN7"/>
     <mergeCell ref="AI4:AN4"/>
-    <mergeCell ref="I15:P15"/>
+    <mergeCell ref="I16:P16"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4365,7 +4364,7 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="8" t="s">
-        <v>174</v>
+        <v>244</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
@@ -4411,7 +4410,7 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J9" s="3"/>
       <c r="K9" s="3"/>
@@ -5993,7 +5992,7 @@
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
       <c r="O5" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
@@ -6253,7 +6252,7 @@
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
       <c r="O10" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
@@ -6349,7 +6348,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
@@ -6357,7 +6356,7 @@
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="2" t="s">
-        <v>215</v>
+        <v>245</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
@@ -6520,7 +6519,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -6624,35 +6623,35 @@
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D4" s="31"/>
       <c r="E4" s="27" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" s="28"/>
       <c r="H4" s="28"/>
       <c r="I4" s="29"/>
       <c r="J4" s="27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K4" s="29"/>
       <c r="L4" s="27" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M4" s="28"/>
       <c r="N4" s="28"/>
       <c r="O4" s="28"/>
       <c r="P4" s="29"/>
       <c r="Q4" s="27" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R4" s="28"/>
       <c r="S4" s="28"/>
       <c r="T4" s="29"/>
       <c r="U4" s="27" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V4" s="28"/>
       <c r="W4" s="28"/>
@@ -6660,21 +6659,21 @@
       <c r="Y4" s="28"/>
       <c r="Z4" s="29"/>
       <c r="AA4" s="27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AB4" s="28"/>
       <c r="AC4" s="28"/>
       <c r="AD4" s="28"/>
       <c r="AE4" s="29"/>
       <c r="AF4" s="27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG4" s="28"/>
       <c r="AH4" s="28"/>
       <c r="AI4" s="28"/>
       <c r="AJ4" s="29"/>
       <c r="AK4" s="27" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL4" s="28"/>
       <c r="AM4" s="28"/>
@@ -6686,35 +6685,35 @@
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
       <c r="I5" s="26"/>
       <c r="J5" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K5" s="26"/>
       <c r="L5" s="19" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
       <c r="T5" s="21"/>
       <c r="U5" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
@@ -6722,21 +6721,21 @@
       <c r="Y5" s="20"/>
       <c r="Z5" s="21"/>
       <c r="AA5" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20"/>
       <c r="AD5" s="20"/>
       <c r="AE5" s="21"/>
       <c r="AF5" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="AG5" s="20"/>
       <c r="AH5" s="20"/>
       <c r="AI5" s="20"/>
       <c r="AJ5" s="21"/>
       <c r="AK5" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
@@ -6752,31 +6751,31 @@
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
       <c r="H6" s="25"/>
       <c r="I6" s="26"/>
       <c r="J6" s="24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="19" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
       <c r="T6" s="21"/>
       <c r="U6" s="19" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
@@ -6784,21 +6783,21 @@
       <c r="Y6" s="20"/>
       <c r="Z6" s="21"/>
       <c r="AA6" s="19" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20"/>
       <c r="AD6" s="20"/>
       <c r="AE6" s="21"/>
       <c r="AF6" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="AG6" s="20"/>
       <c r="AH6" s="20"/>
       <c r="AI6" s="20"/>
       <c r="AJ6" s="21"/>
       <c r="AK6" s="19" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
@@ -6806,7 +6805,7 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -6870,7 +6869,7 @@
   <sheetData>
     <row r="1" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="12" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -6970,39 +6969,39 @@
     </row>
     <row r="4" spans="1:40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="30" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="30" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D4" s="31"/>
       <c r="E4" s="27" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F4" s="28"/>
       <c r="G4" s="28"/>
       <c r="H4" s="28"/>
       <c r="I4" s="29"/>
       <c r="J4" s="27" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="K4" s="29"/>
       <c r="L4" s="27" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M4" s="28"/>
       <c r="N4" s="28"/>
       <c r="O4" s="28"/>
       <c r="P4" s="29"/>
       <c r="Q4" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="R4" s="28"/>
       <c r="S4" s="28"/>
       <c r="T4" s="29"/>
       <c r="U4" s="27" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="V4" s="28"/>
       <c r="W4" s="28"/>
@@ -7010,21 +7009,21 @@
       <c r="Y4" s="28"/>
       <c r="Z4" s="29"/>
       <c r="AA4" s="27" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AB4" s="28"/>
       <c r="AC4" s="28"/>
       <c r="AD4" s="28"/>
       <c r="AE4" s="29"/>
       <c r="AF4" s="27" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AG4" s="28"/>
       <c r="AH4" s="28"/>
       <c r="AI4" s="28"/>
       <c r="AJ4" s="29"/>
       <c r="AK4" s="27" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AL4" s="28"/>
       <c r="AM4" s="28"/>
@@ -7036,35 +7035,35 @@
       </c>
       <c r="B5" s="23"/>
       <c r="C5" s="22" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D5" s="23"/>
       <c r="E5" s="24" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
       <c r="H5" s="25"/>
       <c r="I5" s="26"/>
       <c r="J5" s="24" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="K5" s="26"/>
       <c r="L5" s="19" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="M5" s="20"/>
       <c r="N5" s="20"/>
       <c r="O5" s="20"/>
       <c r="P5" s="21"/>
       <c r="Q5" s="19" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
       <c r="T5" s="21"/>
       <c r="U5" s="19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="V5" s="20"/>
       <c r="W5" s="20"/>
@@ -7072,21 +7071,21 @@
       <c r="Y5" s="20"/>
       <c r="Z5" s="21"/>
       <c r="AA5" s="19" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="AB5" s="20"/>
       <c r="AC5" s="20"/>
       <c r="AD5" s="20"/>
       <c r="AE5" s="21"/>
       <c r="AF5" s="19" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG5" s="20"/>
       <c r="AH5" s="20"/>
       <c r="AI5" s="20"/>
       <c r="AJ5" s="21"/>
       <c r="AK5" s="19" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AL5" s="20"/>
       <c r="AM5" s="20"/>
@@ -7098,35 +7097,35 @@
       </c>
       <c r="B6" s="23"/>
       <c r="C6" s="22" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D6" s="23"/>
       <c r="E6" s="24" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
       <c r="H6" s="25"/>
       <c r="I6" s="26"/>
       <c r="J6" s="24" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="K6" s="26"/>
       <c r="L6" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="M6" s="20"/>
       <c r="N6" s="20"/>
       <c r="O6" s="20"/>
       <c r="P6" s="21"/>
       <c r="Q6" s="19" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
       <c r="T6" s="21"/>
       <c r="U6" s="19" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="V6" s="20"/>
       <c r="W6" s="20"/>
@@ -7134,21 +7133,21 @@
       <c r="Y6" s="20"/>
       <c r="Z6" s="21"/>
       <c r="AA6" s="19" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="AB6" s="20"/>
       <c r="AC6" s="20"/>
       <c r="AD6" s="20"/>
       <c r="AE6" s="21"/>
       <c r="AF6" s="19" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG6" s="20"/>
       <c r="AH6" s="20"/>
       <c r="AI6" s="20"/>
       <c r="AJ6" s="21"/>
       <c r="AK6" s="19" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AL6" s="20"/>
       <c r="AM6" s="20"/>
@@ -7156,7 +7155,7 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
